--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce2a9dd481ca40a5/Desktop/git/secret_stuff_miniapp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{EAA5244A-4873-4B1C-95EB-2450F5CC5E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7AA8C71-2DC2-48CF-9AE3-D6E9E7F954E8}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{EAA5244A-4873-4B1C-95EB-2450F5CC5E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB5154FA-1865-455F-ABE9-9C345FC4ADE6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="293">
   <si>
     <t>id</t>
   </si>
@@ -254,9 +254,6 @@
   </si>
   <si>
     <t>ЗИП-ХУДИ BROKEN PLANET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЗИП-ХУДИ ERD </t>
   </si>
   <si>
     <t>ЗИП-ХУДИ EXTREME CAUSE</t>
@@ -389,9 +386,6 @@
     <t>under1.png,under2.png</t>
   </si>
   <si>
-    <t>red1.png,red2.png</t>
-  </si>
-  <si>
     <t>exctr1.png,exctr2.png</t>
   </si>
   <si>
@@ -659,9 +653,6 @@
     <t>eclnumdop1.png,eclnumdop2.png,eclnumdop3.png,eclnumdop4.png,eclnumdop5.png,eclnumdop6.png,eclnumdop7.png,eclnumdop8.png,eclnumdop9.png,eclnumdop10.png,eclnumdop11.png,eclnumdop12.png,eclnumdop13.png,eclnumdop14.png,eclnumdop15.png</t>
   </si>
   <si>
-    <t>{"белый": {"S":7, "M":1}, "черный": {"S":1}}</t>
-  </si>
-  <si>
     <t>galldop1.png,galldop2.png,galldop3.png,galldop4.png,galldop5.png,galldop6.png,galldop7.png,galldop8.png,galldop9.png,galldop10.png</t>
   </si>
   <si>
@@ -707,9 +698,6 @@
     <t>{"белый": {"M":1, "L":2, "XL":1, "XXL":1}}</t>
   </si>
   <si>
-    <t>{"черный": {"38":1, "42":1, "45":1}, "белый": {"38":2, "39":2, "40":1, "42":2, "46":1}, "серый": {"38":1, "39":1, "43":2}, "коричневый": {"38":1, "39":1, "42":1, "44":1, "45":2}, "голубой": {"38":1}}</t>
-  </si>
-  <si>
     <t>cardgoy1.png,cardgoy2.png,cardgoy3.png,cardgoy4.png,cardgoy5.png</t>
   </si>
   <si>
@@ -764,9 +752,6 @@
     <t>underdop1.png,underdop2.png,underdop3.png,underdop4.png,underdop5.png,underdop6.png,underdop7.png,underdop8.png,underdop9.png,underdop10.png</t>
   </si>
   <si>
-    <t>erddop1.png,erddop2.png,erddop3.png,erddop4.png,erddop5.png,erddop6.png,erddop7.png,erddop8.png</t>
-  </si>
-  <si>
     <t>excstrdop1.png,excstrdop2.png,excstrdop3.png,excstrdop4.png,excstrdop5.png</t>
   </si>
   <si>
@@ -909,6 +894,12 @@
   </si>
   <si>
     <t>protocolnewdop1.png,protocolnewdop2.png,protocolnewdop3.png,protocolnewdop4.png,protocolnewdop5.png,protocolnewdop6.png,protocolnewdop7.png,protocolnewdop8.png,protocolnewdop9.png,protocolnewdop10.png,protocolnewdop11.png</t>
+  </si>
+  <si>
+    <t>{"черный": {"38":1, "42":1, "45":1}, "белый": {"38":2, "39":2,"42":1, "46":1}, "серый": {"38":1, "39":1, "43":2}, "коричневый": {"38":1, "39":1, "42":1, "44":1, "45":2}, "голубой": {"38":1}}</t>
+  </si>
+  <si>
+    <t>{"белый": {"S":7, "M":1}}</t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1144,33 +1135,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1261,16 +1232,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1551,387 +1533,387 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB199"/>
+  <dimension ref="A1:AB196"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="56"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="17" t="s">
+      <c r="F1" s="56"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="I1" s="57"/>
+      <c r="J1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="17" t="s">
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="17" t="s">
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="17" t="s">
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="17" t="s">
+      <c r="X1" s="57"/>
+      <c r="Y1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="18"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="57"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+        <v>278</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="2">
         <v>3699</v>
       </c>
-      <c r="I2" s="60"/>
-      <c r="J2" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
       <c r="O2" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
+        <v>279</v>
+      </c>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
       <c r="S2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="60"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="60"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
       <c r="W2" s="2">
         <v>1</v>
       </c>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
-      <c r="R3" s="60"/>
-      <c r="S3" s="60"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="60"/>
-      <c r="V3" s="60"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="60"/>
-      <c r="Y3" s="60"/>
-      <c r="Z3" s="60"/>
-      <c r="AA3" s="60"/>
-      <c r="AB3" s="60"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="15"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="60"/>
-      <c r="Y4" s="60"/>
-      <c r="Z4" s="60"/>
-      <c r="AA4" s="60"/>
-      <c r="AB4" s="60"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
+        <v>280</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
       <c r="H5" s="2">
         <v>3999</v>
       </c>
-      <c r="I5" s="60"/>
-      <c r="J5" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
       <c r="O5" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
-      <c r="R5" s="60"/>
+        <v>281</v>
+      </c>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
       <c r="S5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="T5" s="60"/>
-      <c r="U5" s="60"/>
-      <c r="V5" s="60"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
       <c r="W5" s="2">
         <v>1</v>
       </c>
-      <c r="X5" s="60"/>
-      <c r="Y5" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="Z5" s="60"/>
-      <c r="AA5" s="60"/>
-      <c r="AB5" s="60"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="60"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="60"/>
-      <c r="U6" s="60"/>
-      <c r="V6" s="60"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="60"/>
-      <c r="Y6" s="60"/>
-      <c r="Z6" s="60"/>
-      <c r="AA6" s="60"/>
-      <c r="AB6" s="60"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="60"/>
-      <c r="U7" s="60"/>
-      <c r="V7" s="60"/>
-      <c r="W7" s="60"/>
-      <c r="X7" s="60"/>
-      <c r="Y7" s="60"/>
-      <c r="Z7" s="60"/>
-      <c r="AA7" s="60"/>
-      <c r="AB7" s="60"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="15"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="30">
+      <c r="A8" s="16">
         <v>3</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="33" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="33">
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="19">
         <v>4299</v>
       </c>
-      <c r="I8" s="35"/>
-      <c r="J8" s="42" t="s">
+      <c r="I8" s="21"/>
+      <c r="J8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="33" t="s">
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="33">
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="19">
         <v>0</v>
       </c>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z8" s="52"/>
-      <c r="AA8" s="52"/>
-      <c r="AB8" s="53"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="39"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="62"/>
-      <c r="M9" s="62"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="61"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="61"/>
-      <c r="U9" s="61"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="54"/>
-      <c r="Z9" s="63"/>
-      <c r="AA9" s="63"/>
-      <c r="AB9" s="56"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="41"/>
+      <c r="AA9" s="41"/>
+      <c r="AB9" s="42"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="32"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="39"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="39"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="57"/>
-      <c r="Z10" s="58"/>
-      <c r="AA10" s="58"/>
-      <c r="AB10" s="59"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="43"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="44"/>
+      <c r="AB10" s="45"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="6"/>
@@ -1944,15 +1926,15 @@
         <v>4299</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="16" t="s">
-        <v>294</v>
+      <c r="J11" s="13" t="s">
+        <v>289</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="6"/>
       <c r="O11" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
@@ -1967,8 +1949,8 @@
         <v>1</v>
       </c>
       <c r="X11" s="6"/>
-      <c r="Y11" s="17" t="s">
-        <v>295</v>
+      <c r="Y11" s="14" t="s">
+        <v>290</v>
       </c>
       <c r="Z11" s="5"/>
       <c r="AA11" s="5"/>
@@ -2039,108 +2021,108 @@
         <v>72</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
+        <v>201</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
       <c r="E14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
       <c r="H14" s="2">
         <v>3299</v>
       </c>
-      <c r="I14" s="60"/>
-      <c r="J14" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="60"/>
-      <c r="N14" s="60"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
       <c r="O14" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="60"/>
+        <v>276</v>
+      </c>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
       <c r="S14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="T14" s="60"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="60"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
       <c r="W14" s="2">
         <v>1</v>
       </c>
-      <c r="X14" s="60"/>
-      <c r="Y14" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z14" s="60"/>
-      <c r="AA14" s="60"/>
-      <c r="AB14" s="60"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="60"/>
-      <c r="V15" s="60"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="60"/>
-      <c r="AA15" s="60"/>
-      <c r="AB15" s="60"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="15"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="60"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="60"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="60"/>
-      <c r="U16" s="60"/>
-      <c r="V16" s="60"/>
-      <c r="W16" s="60"/>
-      <c r="X16" s="60"/>
-      <c r="Y16" s="60"/>
-      <c r="Z16" s="60"/>
-      <c r="AA16" s="60"/>
-      <c r="AB16" s="60"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="15"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15"/>
+      <c r="Z16" s="15"/>
+      <c r="AA16" s="15"/>
+      <c r="AB16" s="15"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -2152,7 +2134,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="6"/>
       <c r="E17" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="6"/>
@@ -2160,15 +2142,15 @@
         <v>1499</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="16" t="s">
-        <v>190</v>
+      <c r="J17" s="13" t="s">
+        <v>188</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6"/>
       <c r="O17" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
@@ -2183,8 +2165,8 @@
         <v>0</v>
       </c>
       <c r="X17" s="6"/>
-      <c r="Y17" s="17" t="s">
-        <v>191</v>
+      <c r="Y17" s="14" t="s">
+        <v>189</v>
       </c>
       <c r="Z17" s="5"/>
       <c r="AA17" s="5"/>
@@ -2251,10 +2233,10 @@
       <c r="AB19" s="12"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
+      <c r="A20" s="58">
         <v>7</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="47" t="s">
         <v>28</v>
       </c>
       <c r="C20" s="5"/>
@@ -2268,7 +2250,7 @@
         <v>3299</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="13" t="s">
         <v>30</v>
       </c>
       <c r="K20" s="5"/>
@@ -2276,7 +2258,7 @@
       <c r="M20" s="5"/>
       <c r="N20" s="6"/>
       <c r="O20" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
@@ -2291,15 +2273,15 @@
         <v>1</v>
       </c>
       <c r="X20" s="6"/>
-      <c r="Y20" s="17" t="s">
-        <v>192</v>
+      <c r="Y20" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="Z20" s="5"/>
       <c r="AA20" s="5"/>
       <c r="AB20" s="6"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
       <c r="D21" s="9"/>
@@ -2329,7 +2311,7 @@
       <c r="AB21" s="9"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
       <c r="D22" s="12"/>
@@ -2368,7 +2350,7 @@
       <c r="C23" s="5"/>
       <c r="D23" s="6"/>
       <c r="E23" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6"/>
@@ -2376,7 +2358,7 @@
         <v>1499</v>
       </c>
       <c r="I23" s="6"/>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="13" t="s">
         <v>33</v>
       </c>
       <c r="K23" s="5"/>
@@ -2384,7 +2366,7 @@
       <c r="M23" s="5"/>
       <c r="N23" s="6"/>
       <c r="O23" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
@@ -2399,8 +2381,8 @@
         <v>0</v>
       </c>
       <c r="X23" s="6"/>
-      <c r="Y23" s="17" t="s">
-        <v>194</v>
+      <c r="Y23" s="14" t="s">
+        <v>192</v>
       </c>
       <c r="Z23" s="5"/>
       <c r="AA23" s="5"/>
@@ -2476,7 +2458,7 @@
       <c r="C26" s="5"/>
       <c r="D26" s="6"/>
       <c r="E26" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6"/>
@@ -2484,7 +2466,7 @@
         <v>1499</v>
       </c>
       <c r="I26" s="6"/>
-      <c r="J26" s="16" t="s">
+      <c r="J26" s="13" t="s">
         <v>35</v>
       </c>
       <c r="K26" s="5"/>
@@ -2492,7 +2474,7 @@
       <c r="M26" s="5"/>
       <c r="N26" s="6"/>
       <c r="O26" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
@@ -2507,8 +2489,8 @@
         <v>0</v>
       </c>
       <c r="X26" s="6"/>
-      <c r="Y26" s="17" t="s">
-        <v>196</v>
+      <c r="Y26" s="14" t="s">
+        <v>194</v>
       </c>
       <c r="Z26" s="5"/>
       <c r="AA26" s="5"/>
@@ -2584,7 +2566,7 @@
       <c r="C29" s="5"/>
       <c r="D29" s="6"/>
       <c r="E29" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6"/>
@@ -2592,7 +2574,7 @@
         <v>1299</v>
       </c>
       <c r="I29" s="6"/>
-      <c r="J29" s="16" t="s">
+      <c r="J29" s="13" t="s">
         <v>36</v>
       </c>
       <c r="K29" s="5"/>
@@ -2600,7 +2582,7 @@
       <c r="M29" s="5"/>
       <c r="N29" s="6"/>
       <c r="O29" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
@@ -2615,8 +2597,8 @@
         <v>0</v>
       </c>
       <c r="X29" s="6"/>
-      <c r="Y29" s="17" t="s">
-        <v>198</v>
+      <c r="Y29" s="14" t="s">
+        <v>196</v>
       </c>
       <c r="Z29" s="5"/>
       <c r="AA29" s="5"/>
@@ -2692,7 +2674,7 @@
       <c r="C32" s="5"/>
       <c r="D32" s="6"/>
       <c r="E32" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6"/>
@@ -2700,7 +2682,7 @@
         <v>1199</v>
       </c>
       <c r="I32" s="6"/>
-      <c r="J32" s="16" t="s">
+      <c r="J32" s="13" t="s">
         <v>38</v>
       </c>
       <c r="K32" s="5"/>
@@ -2708,7 +2690,7 @@
       <c r="M32" s="5"/>
       <c r="N32" s="6"/>
       <c r="O32" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
@@ -2723,8 +2705,8 @@
         <v>0</v>
       </c>
       <c r="X32" s="6"/>
-      <c r="Y32" s="17" t="s">
-        <v>200</v>
+      <c r="Y32" s="14" t="s">
+        <v>198</v>
       </c>
       <c r="Z32" s="5"/>
       <c r="AA32" s="5"/>
@@ -2808,7 +2790,7 @@
         <v>3299</v>
       </c>
       <c r="I35" s="6"/>
-      <c r="J35" s="16" t="s">
+      <c r="J35" s="13" t="s">
         <v>40</v>
       </c>
       <c r="K35" s="5"/>
@@ -2816,7 +2798,7 @@
       <c r="M35" s="5"/>
       <c r="N35" s="6"/>
       <c r="O35" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
@@ -2831,8 +2813,8 @@
         <v>0</v>
       </c>
       <c r="X35" s="6"/>
-      <c r="Y35" s="17" t="s">
-        <v>206</v>
+      <c r="Y35" s="14" t="s">
+        <v>204</v>
       </c>
       <c r="Z35" s="5"/>
       <c r="AA35" s="5"/>
@@ -2916,15 +2898,15 @@
         <v>3799</v>
       </c>
       <c r="I38" s="6"/>
-      <c r="J38" s="16" t="s">
-        <v>217</v>
+      <c r="J38" s="13" t="s">
+        <v>214</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="6"/>
       <c r="O38" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
@@ -2939,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="X38" s="6"/>
-      <c r="Y38" s="17" t="s">
+      <c r="Y38" s="14" t="s">
         <v>43</v>
       </c>
       <c r="Z38" s="5"/>
@@ -3024,7 +3006,7 @@
         <v>3999</v>
       </c>
       <c r="I41" s="6"/>
-      <c r="J41" s="16" t="s">
+      <c r="J41" s="13" t="s">
         <v>44</v>
       </c>
       <c r="K41" s="5"/>
@@ -3032,7 +3014,7 @@
       <c r="M41" s="5"/>
       <c r="N41" s="6"/>
       <c r="O41" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
@@ -3047,8 +3029,8 @@
         <v>1</v>
       </c>
       <c r="X41" s="6"/>
-      <c r="Y41" s="17" t="s">
-        <v>208</v>
+      <c r="Y41" s="14" t="s">
+        <v>206</v>
       </c>
       <c r="Z41" s="5"/>
       <c r="AA41" s="5"/>
@@ -3132,7 +3114,7 @@
         <v>2699</v>
       </c>
       <c r="I44" s="6"/>
-      <c r="J44" s="16" t="s">
+      <c r="J44" s="13" t="s">
         <v>46</v>
       </c>
       <c r="K44" s="5"/>
@@ -3140,7 +3122,7 @@
       <c r="M44" s="5"/>
       <c r="N44" s="6"/>
       <c r="O44" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
@@ -3155,8 +3137,8 @@
         <v>1</v>
       </c>
       <c r="X44" s="6"/>
-      <c r="Y44" s="17" t="s">
-        <v>210</v>
+      <c r="Y44" s="14" t="s">
+        <v>208</v>
       </c>
       <c r="Z44" s="5"/>
       <c r="AA44" s="5"/>
@@ -3226,7 +3208,7 @@
       <c r="A47" s="2">
         <v>17</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="47" t="s">
         <v>47</v>
       </c>
       <c r="C47" s="5"/>
@@ -3240,7 +3222,7 @@
         <v>4999</v>
       </c>
       <c r="I47" s="6"/>
-      <c r="J47" s="16" t="s">
+      <c r="J47" s="13" t="s">
         <v>48</v>
       </c>
       <c r="K47" s="5"/>
@@ -3248,7 +3230,7 @@
       <c r="M47" s="5"/>
       <c r="N47" s="6"/>
       <c r="O47" s="2" t="s">
-        <v>228</v>
+        <v>291</v>
       </c>
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
@@ -3263,8 +3245,8 @@
         <v>1</v>
       </c>
       <c r="X47" s="6"/>
-      <c r="Y47" s="17" t="s">
-        <v>211</v>
+      <c r="Y47" s="14" t="s">
+        <v>209</v>
       </c>
       <c r="Z47" s="5"/>
       <c r="AA47" s="5"/>
@@ -3348,7 +3330,7 @@
         <v>1499</v>
       </c>
       <c r="I50" s="6"/>
-      <c r="J50" s="16" t="s">
+      <c r="J50" s="13" t="s">
         <v>50</v>
       </c>
       <c r="K50" s="5"/>
@@ -3356,7 +3338,7 @@
       <c r="M50" s="5"/>
       <c r="N50" s="6"/>
       <c r="O50" s="2" t="s">
-        <v>212</v>
+        <v>292</v>
       </c>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
@@ -3371,8 +3353,8 @@
         <v>0</v>
       </c>
       <c r="X50" s="6"/>
-      <c r="Y50" s="17" t="s">
-        <v>213</v>
+      <c r="Y50" s="14" t="s">
+        <v>210</v>
       </c>
       <c r="Z50" s="5"/>
       <c r="AA50" s="5"/>
@@ -3442,11 +3424,11 @@
       <c r="A53" s="2">
         <v>19</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="C53" s="21"/>
-      <c r="D53" s="22"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="49"/>
       <c r="E53" s="2" t="s">
         <v>18</v>
       </c>
@@ -3456,15 +3438,15 @@
         <v>2299</v>
       </c>
       <c r="I53" s="6"/>
-      <c r="J53" s="16" t="s">
-        <v>107</v>
+      <c r="J53" s="13" t="s">
+        <v>106</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="6"/>
       <c r="O53" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
@@ -3479,8 +3461,8 @@
         <v>0</v>
       </c>
       <c r="X53" s="6"/>
-      <c r="Y53" s="17" t="s">
-        <v>214</v>
+      <c r="Y53" s="14" t="s">
+        <v>211</v>
       </c>
       <c r="Z53" s="5"/>
       <c r="AA53" s="5"/>
@@ -3488,9 +3470,9 @@
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="25"/>
+      <c r="B54" s="50"/>
+      <c r="C54" s="51"/>
+      <c r="D54" s="52"/>
       <c r="E54" s="7"/>
       <c r="F54" s="8"/>
       <c r="G54" s="9"/>
@@ -3518,9 +3500,9 @@
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="28"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="55"/>
       <c r="E55" s="10"/>
       <c r="F55" s="11"/>
       <c r="G55" s="12"/>
@@ -3564,7 +3546,7 @@
         <v>2299</v>
       </c>
       <c r="I56" s="6"/>
-      <c r="J56" s="16" t="s">
+      <c r="J56" s="13" t="s">
         <v>52</v>
       </c>
       <c r="K56" s="5"/>
@@ -3572,7 +3554,7 @@
       <c r="M56" s="5"/>
       <c r="N56" s="6"/>
       <c r="O56" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
@@ -3587,8 +3569,8 @@
         <v>0</v>
       </c>
       <c r="X56" s="6"/>
-      <c r="Y56" s="17" t="s">
-        <v>216</v>
+      <c r="Y56" s="14" t="s">
+        <v>213</v>
       </c>
       <c r="Z56" s="5"/>
       <c r="AA56" s="5"/>
@@ -3672,7 +3654,7 @@
         <v>2999</v>
       </c>
       <c r="I59" s="6"/>
-      <c r="J59" s="16" t="s">
+      <c r="J59" s="13" t="s">
         <v>54</v>
       </c>
       <c r="K59" s="5"/>
@@ -3680,7 +3662,7 @@
       <c r="M59" s="5"/>
       <c r="N59" s="6"/>
       <c r="O59" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
@@ -3695,8 +3677,8 @@
         <v>0</v>
       </c>
       <c r="X59" s="6"/>
-      <c r="Y59" s="17" t="s">
-        <v>219</v>
+      <c r="Y59" s="14" t="s">
+        <v>216</v>
       </c>
       <c r="Z59" s="5"/>
       <c r="AA59" s="5"/>
@@ -3772,7 +3754,7 @@
       <c r="C62" s="5"/>
       <c r="D62" s="6"/>
       <c r="E62" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="6"/>
@@ -3780,15 +3762,15 @@
         <v>1999</v>
       </c>
       <c r="I62" s="6"/>
-      <c r="J62" s="16" t="s">
-        <v>221</v>
+      <c r="J62" s="13" t="s">
+        <v>218</v>
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
       <c r="N62" s="6"/>
       <c r="O62" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P62" s="5"/>
       <c r="Q62" s="5"/>
@@ -3803,8 +3785,8 @@
         <v>0</v>
       </c>
       <c r="X62" s="6"/>
-      <c r="Y62" s="17" t="s">
-        <v>222</v>
+      <c r="Y62" s="14" t="s">
+        <v>219</v>
       </c>
       <c r="Z62" s="5"/>
       <c r="AA62" s="5"/>
@@ -3888,15 +3870,15 @@
         <v>1999</v>
       </c>
       <c r="I65" s="6"/>
-      <c r="J65" s="16" t="s">
-        <v>224</v>
+      <c r="J65" s="13" t="s">
+        <v>221</v>
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="6"/>
       <c r="O65" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P65" s="5"/>
       <c r="Q65" s="5"/>
@@ -3911,8 +3893,8 @@
         <v>0</v>
       </c>
       <c r="X65" s="6"/>
-      <c r="Y65" s="17" t="s">
-        <v>225</v>
+      <c r="Y65" s="14" t="s">
+        <v>222</v>
       </c>
       <c r="Z65" s="5"/>
       <c r="AA65" s="5"/>
@@ -3996,15 +3978,15 @@
         <v>1799</v>
       </c>
       <c r="I68" s="6"/>
-      <c r="J68" s="16" t="s">
-        <v>108</v>
+      <c r="J68" s="13" t="s">
+        <v>107</v>
       </c>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="5"/>
       <c r="N68" s="6"/>
       <c r="O68" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P68" s="5"/>
       <c r="Q68" s="5"/>
@@ -4019,8 +4001,8 @@
         <v>0</v>
       </c>
       <c r="X68" s="6"/>
-      <c r="Y68" s="17" t="s">
-        <v>226</v>
+      <c r="Y68" s="14" t="s">
+        <v>223</v>
       </c>
       <c r="Z68" s="5"/>
       <c r="AA68" s="5"/>
@@ -4104,15 +4086,15 @@
         <v>699</v>
       </c>
       <c r="I71" s="6"/>
-      <c r="J71" s="16" t="s">
-        <v>146</v>
+      <c r="J71" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
       <c r="N71" s="6"/>
       <c r="O71" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
@@ -4127,8 +4109,8 @@
         <v>0</v>
       </c>
       <c r="X71" s="6"/>
-      <c r="Y71" s="17" t="s">
-        <v>229</v>
+      <c r="Y71" s="14" t="s">
+        <v>225</v>
       </c>
       <c r="Z71" s="5"/>
       <c r="AA71" s="5"/>
@@ -4212,15 +4194,15 @@
         <v>1799</v>
       </c>
       <c r="I74" s="6"/>
-      <c r="J74" s="16" t="s">
-        <v>109</v>
+      <c r="J74" s="13" t="s">
+        <v>108</v>
       </c>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
       <c r="N74" s="6"/>
       <c r="O74" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
@@ -4235,8 +4217,8 @@
         <v>0</v>
       </c>
       <c r="X74" s="6"/>
-      <c r="Y74" s="17" t="s">
-        <v>231</v>
+      <c r="Y74" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="Z74" s="5"/>
       <c r="AA74" s="5"/>
@@ -4320,15 +4302,15 @@
         <v>1899</v>
       </c>
       <c r="I77" s="6"/>
-      <c r="J77" s="16" t="s">
-        <v>110</v>
+      <c r="J77" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
       <c r="N77" s="6"/>
       <c r="O77" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
@@ -4343,8 +4325,8 @@
         <v>0</v>
       </c>
       <c r="X77" s="6"/>
-      <c r="Y77" s="17" t="s">
-        <v>233</v>
+      <c r="Y77" s="14" t="s">
+        <v>229</v>
       </c>
       <c r="Z77" s="5"/>
       <c r="AA77" s="5"/>
@@ -4420,7 +4402,7 @@
       <c r="C80" s="5"/>
       <c r="D80" s="6"/>
       <c r="E80" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="6"/>
@@ -4428,15 +4410,15 @@
         <v>1499</v>
       </c>
       <c r="I80" s="6"/>
-      <c r="J80" s="16" t="s">
-        <v>111</v>
+      <c r="J80" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="K80" s="5"/>
       <c r="L80" s="5"/>
       <c r="M80" s="5"/>
       <c r="N80" s="6"/>
       <c r="O80" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
@@ -4451,8 +4433,8 @@
         <v>0</v>
       </c>
       <c r="X80" s="6"/>
-      <c r="Y80" s="17" t="s">
-        <v>234</v>
+      <c r="Y80" s="14" t="s">
+        <v>230</v>
       </c>
       <c r="Z80" s="5"/>
       <c r="AA80" s="5"/>
@@ -4528,7 +4510,7 @@
       <c r="C83" s="5"/>
       <c r="D83" s="6"/>
       <c r="E83" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="6"/>
@@ -4536,15 +4518,15 @@
         <v>2299</v>
       </c>
       <c r="I83" s="6"/>
-      <c r="J83" s="16" t="s">
-        <v>112</v>
+      <c r="J83" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="5"/>
       <c r="N83" s="6"/>
       <c r="O83" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
@@ -4559,8 +4541,8 @@
         <v>0</v>
       </c>
       <c r="X83" s="6"/>
-      <c r="Y83" s="17" t="s">
-        <v>235</v>
+      <c r="Y83" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="Z83" s="5"/>
       <c r="AA83" s="5"/>
@@ -4636,7 +4618,7 @@
       <c r="C86" s="5"/>
       <c r="D86" s="6"/>
       <c r="E86" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="6"/>
@@ -4644,15 +4626,15 @@
         <v>1499</v>
       </c>
       <c r="I86" s="6"/>
-      <c r="J86" s="16" t="s">
-        <v>113</v>
+      <c r="J86" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
       <c r="N86" s="6"/>
       <c r="O86" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
@@ -4667,8 +4649,8 @@
         <v>0</v>
       </c>
       <c r="X86" s="6"/>
-      <c r="Y86" s="17" t="s">
-        <v>236</v>
+      <c r="Y86" s="14" t="s">
+        <v>232</v>
       </c>
       <c r="Z86" s="5"/>
       <c r="AA86" s="5"/>
@@ -4738,8 +4720,8 @@
       <c r="A89" s="2">
         <v>32</v>
       </c>
-      <c r="B89" s="29" t="s">
-        <v>114</v>
+      <c r="B89" s="46" t="s">
+        <v>113</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="6"/>
@@ -4752,15 +4734,15 @@
         <v>1399</v>
       </c>
       <c r="I89" s="6"/>
-      <c r="J89" s="16" t="s">
-        <v>115</v>
+      <c r="J89" s="13" t="s">
+        <v>114</v>
       </c>
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
       <c r="N89" s="6"/>
       <c r="O89" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
@@ -4775,8 +4757,8 @@
         <v>0</v>
       </c>
       <c r="X89" s="6"/>
-      <c r="Y89" s="17" t="s">
-        <v>240</v>
+      <c r="Y89" s="14" t="s">
+        <v>236</v>
       </c>
       <c r="Z89" s="5"/>
       <c r="AA89" s="5"/>
@@ -4860,15 +4842,15 @@
         <v>1999</v>
       </c>
       <c r="I92" s="6"/>
-      <c r="J92" s="16" t="s">
-        <v>116</v>
+      <c r="J92" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="K92" s="5"/>
       <c r="L92" s="5"/>
       <c r="M92" s="5"/>
       <c r="N92" s="6"/>
       <c r="O92" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
@@ -4883,8 +4865,8 @@
         <v>0</v>
       </c>
       <c r="X92" s="6"/>
-      <c r="Y92" s="17" t="s">
-        <v>241</v>
+      <c r="Y92" s="14" t="s">
+        <v>237</v>
       </c>
       <c r="Z92" s="5"/>
       <c r="AA92" s="5"/>
@@ -4968,15 +4950,15 @@
         <v>1499</v>
       </c>
       <c r="I95" s="6"/>
-      <c r="J95" s="16" t="s">
-        <v>117</v>
+      <c r="J95" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="K95" s="5"/>
       <c r="L95" s="5"/>
       <c r="M95" s="5"/>
       <c r="N95" s="6"/>
       <c r="O95" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
@@ -4991,8 +4973,8 @@
         <v>0</v>
       </c>
       <c r="X95" s="6"/>
-      <c r="Y95" s="17" t="s">
-        <v>242</v>
+      <c r="Y95" s="14" t="s">
+        <v>238</v>
       </c>
       <c r="Z95" s="5"/>
       <c r="AA95" s="5"/>
@@ -5076,15 +5058,15 @@
         <v>4999</v>
       </c>
       <c r="I98" s="6"/>
-      <c r="J98" s="16" t="s">
-        <v>118</v>
+      <c r="J98" s="13" t="s">
+        <v>117</v>
       </c>
       <c r="K98" s="5"/>
       <c r="L98" s="5"/>
       <c r="M98" s="5"/>
       <c r="N98" s="6"/>
       <c r="O98" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
@@ -5099,8 +5081,8 @@
         <v>1</v>
       </c>
       <c r="X98" s="6"/>
-      <c r="Y98" s="17" t="s">
-        <v>243</v>
+      <c r="Y98" s="14" t="s">
+        <v>239</v>
       </c>
       <c r="Z98" s="5"/>
       <c r="AA98" s="5"/>
@@ -5184,15 +5166,15 @@
         <v>4999</v>
       </c>
       <c r="I101" s="6"/>
-      <c r="J101" s="16" t="s">
-        <v>119</v>
+      <c r="J101" s="13" t="s">
+        <v>118</v>
       </c>
       <c r="K101" s="5"/>
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
       <c r="N101" s="6"/>
       <c r="O101" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
@@ -5207,8 +5189,8 @@
         <v>1</v>
       </c>
       <c r="X101" s="6"/>
-      <c r="Y101" s="17" t="s">
-        <v>244</v>
+      <c r="Y101" s="14" t="s">
+        <v>240</v>
       </c>
       <c r="Z101" s="5"/>
       <c r="AA101" s="5"/>
@@ -5292,15 +5274,15 @@
         <v>2999</v>
       </c>
       <c r="I104" s="6"/>
-      <c r="J104" s="16" t="s">
-        <v>120</v>
+      <c r="J104" s="13" t="s">
+        <v>119</v>
       </c>
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
       <c r="N104" s="6"/>
       <c r="O104" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
@@ -5315,8 +5297,8 @@
         <v>0</v>
       </c>
       <c r="X104" s="6"/>
-      <c r="Y104" s="17" t="s">
-        <v>245</v>
+      <c r="Y104" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="Z104" s="5"/>
       <c r="AA104" s="5"/>
@@ -5400,15 +5382,15 @@
         <v>3699</v>
       </c>
       <c r="I107" s="6"/>
-      <c r="J107" s="16" t="s">
-        <v>121</v>
+      <c r="J107" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="K107" s="5"/>
       <c r="L107" s="5"/>
       <c r="M107" s="5"/>
       <c r="N107" s="6"/>
       <c r="O107" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
@@ -5423,8 +5405,8 @@
         <v>0</v>
       </c>
       <c r="X107" s="6"/>
-      <c r="Y107" s="17" t="s">
-        <v>246</v>
+      <c r="Y107" s="14" t="s">
+        <v>242</v>
       </c>
       <c r="Z107" s="5"/>
       <c r="AA107" s="5"/>
@@ -5492,7 +5474,7 @@
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>78</v>
@@ -5508,15 +5490,15 @@
         <v>2999</v>
       </c>
       <c r="I110" s="6"/>
-      <c r="J110" s="16" t="s">
-        <v>122</v>
+      <c r="J110" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="5"/>
       <c r="N110" s="6"/>
       <c r="O110" s="2" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
       <c r="P110" s="5"/>
       <c r="Q110" s="5"/>
@@ -5531,8 +5513,8 @@
         <v>0</v>
       </c>
       <c r="X110" s="6"/>
-      <c r="Y110" s="17" t="s">
-        <v>247</v>
+      <c r="Y110" s="14" t="s">
+        <v>243</v>
       </c>
       <c r="Z110" s="5"/>
       <c r="AA110" s="5"/>
@@ -5600,7 +5582,7 @@
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>79</v>
@@ -5613,18 +5595,18 @@
       <c r="F113" s="5"/>
       <c r="G113" s="6"/>
       <c r="H113" s="2">
-        <v>2999</v>
+        <v>2699</v>
       </c>
       <c r="I113" s="6"/>
-      <c r="J113" s="16" t="s">
-        <v>123</v>
+      <c r="J113" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="5"/>
       <c r="N113" s="6"/>
       <c r="O113" s="2" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="P113" s="5"/>
       <c r="Q113" s="5"/>
@@ -5639,8 +5621,8 @@
         <v>0</v>
       </c>
       <c r="X113" s="6"/>
-      <c r="Y113" s="17" t="s">
-        <v>248</v>
+      <c r="Y113" s="14" t="s">
+        <v>245</v>
       </c>
       <c r="Z113" s="5"/>
       <c r="AA113" s="5"/>
@@ -5708,7 +5690,7 @@
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>80</v>
@@ -5721,18 +5703,18 @@
       <c r="F116" s="5"/>
       <c r="G116" s="6"/>
       <c r="H116" s="2">
-        <v>2699</v>
+        <v>2899</v>
       </c>
       <c r="I116" s="6"/>
-      <c r="J116" s="16" t="s">
-        <v>124</v>
+      <c r="J116" s="13" t="s">
+        <v>143</v>
       </c>
       <c r="K116" s="5"/>
       <c r="L116" s="5"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
       <c r="O116" s="2" t="s">
-        <v>249</v>
+        <v>164</v>
       </c>
       <c r="P116" s="5"/>
       <c r="Q116" s="5"/>
@@ -5747,8 +5729,8 @@
         <v>0</v>
       </c>
       <c r="X116" s="6"/>
-      <c r="Y116" s="17" t="s">
-        <v>250</v>
+      <c r="Y116" s="14" t="s">
+        <v>246</v>
       </c>
       <c r="Z116" s="5"/>
       <c r="AA116" s="5"/>
@@ -5816,7 +5798,7 @@
     </row>
     <row r="119" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>81</v>
@@ -5829,18 +5811,18 @@
       <c r="F119" s="5"/>
       <c r="G119" s="6"/>
       <c r="H119" s="2">
-        <v>2899</v>
+        <v>3799</v>
       </c>
       <c r="I119" s="6"/>
-      <c r="J119" s="16" t="s">
-        <v>145</v>
+      <c r="J119" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
       <c r="N119" s="6"/>
       <c r="O119" s="2" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
@@ -5855,8 +5837,8 @@
         <v>0</v>
       </c>
       <c r="X119" s="6"/>
-      <c r="Y119" s="17" t="s">
-        <v>251</v>
+      <c r="Y119" s="14" t="s">
+        <v>247</v>
       </c>
       <c r="Z119" s="5"/>
       <c r="AA119" s="5"/>
@@ -5923,222 +5905,222 @@
       <c r="AB121" s="12"/>
     </row>
     <row r="122" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
-        <v>47</v>
-      </c>
-      <c r="B122" s="2" t="s">
+      <c r="A122" s="16">
+        <v>48</v>
+      </c>
+      <c r="B122" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C122" s="5"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="2" t="s">
+      <c r="C122" s="20"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F122" s="5"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="2">
-        <v>3799</v>
-      </c>
-      <c r="I122" s="6"/>
-      <c r="J122" s="16" t="s">
+      <c r="F122" s="20"/>
+      <c r="G122" s="21"/>
+      <c r="H122" s="19">
+        <v>1499</v>
+      </c>
+      <c r="I122" s="21"/>
+      <c r="J122" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="K122" s="29"/>
+      <c r="L122" s="29"/>
+      <c r="M122" s="29"/>
+      <c r="N122" s="30"/>
+      <c r="O122" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="P122" s="20"/>
+      <c r="Q122" s="20"/>
+      <c r="R122" s="21"/>
+      <c r="S122" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="T122" s="20"/>
+      <c r="U122" s="20"/>
+      <c r="V122" s="21"/>
+      <c r="W122" s="19">
+        <v>0</v>
+      </c>
+      <c r="X122" s="21"/>
+      <c r="Y122" s="37"/>
+      <c r="Z122" s="38"/>
+      <c r="AA122" s="38"/>
+      <c r="AB122" s="39"/>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A123" s="17"/>
+      <c r="B123" s="22"/>
+      <c r="C123" s="23"/>
+      <c r="D123" s="24"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="23"/>
+      <c r="G123" s="24"/>
+      <c r="H123" s="22"/>
+      <c r="I123" s="24"/>
+      <c r="J123" s="31"/>
+      <c r="K123" s="32"/>
+      <c r="L123" s="32"/>
+      <c r="M123" s="32"/>
+      <c r="N123" s="33"/>
+      <c r="O123" s="22"/>
+      <c r="P123" s="23"/>
+      <c r="Q123" s="23"/>
+      <c r="R123" s="24"/>
+      <c r="S123" s="22"/>
+      <c r="T123" s="23"/>
+      <c r="U123" s="23"/>
+      <c r="V123" s="24"/>
+      <c r="W123" s="22"/>
+      <c r="X123" s="24"/>
+      <c r="Y123" s="40"/>
+      <c r="Z123" s="41"/>
+      <c r="AA123" s="41"/>
+      <c r="AB123" s="42"/>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A124" s="18"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="26"/>
+      <c r="D124" s="27"/>
+      <c r="E124" s="25"/>
+      <c r="F124" s="26"/>
+      <c r="G124" s="27"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="27"/>
+      <c r="J124" s="34"/>
+      <c r="K124" s="35"/>
+      <c r="L124" s="35"/>
+      <c r="M124" s="35"/>
+      <c r="N124" s="36"/>
+      <c r="O124" s="25"/>
+      <c r="P124" s="26"/>
+      <c r="Q124" s="26"/>
+      <c r="R124" s="27"/>
+      <c r="S124" s="25"/>
+      <c r="T124" s="26"/>
+      <c r="U124" s="26"/>
+      <c r="V124" s="27"/>
+      <c r="W124" s="25"/>
+      <c r="X124" s="27"/>
+      <c r="Y124" s="43"/>
+      <c r="Z124" s="44"/>
+      <c r="AA124" s="44"/>
+      <c r="AB124" s="45"/>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A125" s="2">
+        <v>49</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C125" s="5"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F125" s="5"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="2">
+        <v>3899</v>
+      </c>
+      <c r="I125" s="6"/>
+      <c r="J125" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="K122" s="5"/>
-      <c r="L122" s="5"/>
-      <c r="M122" s="5"/>
-      <c r="N122" s="6"/>
-      <c r="O122" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="P122" s="5"/>
-      <c r="Q122" s="5"/>
-      <c r="R122" s="6"/>
-      <c r="S122" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T122" s="5"/>
-      <c r="U122" s="5"/>
-      <c r="V122" s="6"/>
-      <c r="W122" s="2">
-        <v>0</v>
-      </c>
-      <c r="X122" s="6"/>
-      <c r="Y122" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z122" s="5"/>
-      <c r="AA122" s="5"/>
-      <c r="AB122" s="6"/>
-    </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A123" s="3"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="9"/>
-      <c r="J123" s="7"/>
-      <c r="K123" s="8"/>
-      <c r="L123" s="8"/>
-      <c r="M123" s="8"/>
-      <c r="N123" s="9"/>
-      <c r="O123" s="7"/>
-      <c r="P123" s="8"/>
-      <c r="Q123" s="8"/>
-      <c r="R123" s="9"/>
-      <c r="S123" s="7"/>
-      <c r="T123" s="8"/>
-      <c r="U123" s="8"/>
-      <c r="V123" s="9"/>
-      <c r="W123" s="7"/>
-      <c r="X123" s="9"/>
-      <c r="Y123" s="7"/>
-      <c r="Z123" s="8"/>
-      <c r="AA123" s="8"/>
-      <c r="AB123" s="9"/>
-    </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A124" s="4"/>
-      <c r="B124" s="10"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="12"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="11"/>
-      <c r="G124" s="12"/>
-      <c r="H124" s="10"/>
-      <c r="I124" s="12"/>
-      <c r="J124" s="10"/>
-      <c r="K124" s="11"/>
-      <c r="L124" s="11"/>
-      <c r="M124" s="11"/>
-      <c r="N124" s="12"/>
-      <c r="O124" s="10"/>
-      <c r="P124" s="11"/>
-      <c r="Q124" s="11"/>
-      <c r="R124" s="12"/>
-      <c r="S124" s="10"/>
-      <c r="T124" s="11"/>
-      <c r="U124" s="11"/>
-      <c r="V124" s="12"/>
-      <c r="W124" s="10"/>
-      <c r="X124" s="12"/>
-      <c r="Y124" s="10"/>
-      <c r="Z124" s="11"/>
-      <c r="AA124" s="11"/>
-      <c r="AB124" s="12"/>
-    </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A125" s="30">
-        <v>48</v>
-      </c>
-      <c r="B125" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C125" s="34"/>
-      <c r="D125" s="35"/>
-      <c r="E125" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="F125" s="34"/>
-      <c r="G125" s="35"/>
-      <c r="H125" s="33">
-        <v>1499</v>
-      </c>
-      <c r="I125" s="35"/>
-      <c r="J125" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="K125" s="43"/>
-      <c r="L125" s="43"/>
-      <c r="M125" s="43"/>
-      <c r="N125" s="44"/>
-      <c r="O125" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="P125" s="34"/>
-      <c r="Q125" s="34"/>
-      <c r="R125" s="35"/>
-      <c r="S125" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="T125" s="34"/>
-      <c r="U125" s="34"/>
-      <c r="V125" s="35"/>
-      <c r="W125" s="33">
-        <v>0</v>
-      </c>
-      <c r="X125" s="35"/>
-      <c r="Y125" s="51"/>
-      <c r="Z125" s="52"/>
-      <c r="AA125" s="52"/>
-      <c r="AB125" s="53"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="5"/>
+      <c r="M125" s="5"/>
+      <c r="N125" s="6"/>
+      <c r="O125" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="P125" s="5"/>
+      <c r="Q125" s="5"/>
+      <c r="R125" s="6"/>
+      <c r="S125" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T125" s="5"/>
+      <c r="U125" s="5"/>
+      <c r="V125" s="6"/>
+      <c r="W125" s="2">
+        <v>1</v>
+      </c>
+      <c r="X125" s="6"/>
+      <c r="Y125" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z125" s="5"/>
+      <c r="AA125" s="5"/>
+      <c r="AB125" s="6"/>
     </row>
     <row r="126" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A126" s="31"/>
-      <c r="B126" s="36"/>
-      <c r="C126" s="37"/>
-      <c r="D126" s="38"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="37"/>
-      <c r="G126" s="38"/>
-      <c r="H126" s="36"/>
-      <c r="I126" s="38"/>
-      <c r="J126" s="45"/>
-      <c r="K126" s="46"/>
-      <c r="L126" s="46"/>
-      <c r="M126" s="46"/>
-      <c r="N126" s="47"/>
-      <c r="O126" s="36"/>
-      <c r="P126" s="37"/>
-      <c r="Q126" s="37"/>
-      <c r="R126" s="38"/>
-      <c r="S126" s="36"/>
-      <c r="T126" s="37"/>
-      <c r="U126" s="37"/>
-      <c r="V126" s="38"/>
-      <c r="W126" s="36"/>
-      <c r="X126" s="38"/>
-      <c r="Y126" s="54"/>
-      <c r="Z126" s="55"/>
-      <c r="AA126" s="55"/>
-      <c r="AB126" s="56"/>
+      <c r="A126" s="3"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="9"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="8"/>
+      <c r="G126" s="9"/>
+      <c r="H126" s="7"/>
+      <c r="I126" s="9"/>
+      <c r="J126" s="7"/>
+      <c r="K126" s="8"/>
+      <c r="L126" s="8"/>
+      <c r="M126" s="8"/>
+      <c r="N126" s="9"/>
+      <c r="O126" s="7"/>
+      <c r="P126" s="8"/>
+      <c r="Q126" s="8"/>
+      <c r="R126" s="9"/>
+      <c r="S126" s="7"/>
+      <c r="T126" s="8"/>
+      <c r="U126" s="8"/>
+      <c r="V126" s="9"/>
+      <c r="W126" s="7"/>
+      <c r="X126" s="9"/>
+      <c r="Y126" s="7"/>
+      <c r="Z126" s="8"/>
+      <c r="AA126" s="8"/>
+      <c r="AB126" s="9"/>
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A127" s="32"/>
-      <c r="B127" s="39"/>
-      <c r="C127" s="40"/>
-      <c r="D127" s="41"/>
-      <c r="E127" s="39"/>
-      <c r="F127" s="40"/>
-      <c r="G127" s="41"/>
-      <c r="H127" s="39"/>
-      <c r="I127" s="41"/>
-      <c r="J127" s="48"/>
-      <c r="K127" s="49"/>
-      <c r="L127" s="49"/>
-      <c r="M127" s="49"/>
-      <c r="N127" s="50"/>
-      <c r="O127" s="39"/>
-      <c r="P127" s="40"/>
-      <c r="Q127" s="40"/>
-      <c r="R127" s="41"/>
-      <c r="S127" s="39"/>
-      <c r="T127" s="40"/>
-      <c r="U127" s="40"/>
-      <c r="V127" s="41"/>
-      <c r="W127" s="39"/>
-      <c r="X127" s="41"/>
-      <c r="Y127" s="57"/>
-      <c r="Z127" s="58"/>
-      <c r="AA127" s="58"/>
-      <c r="AB127" s="59"/>
+      <c r="A127" s="4"/>
+      <c r="B127" s="10"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="10"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="12"/>
+      <c r="H127" s="10"/>
+      <c r="I127" s="12"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="11"/>
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+      <c r="N127" s="12"/>
+      <c r="O127" s="10"/>
+      <c r="P127" s="11"/>
+      <c r="Q127" s="11"/>
+      <c r="R127" s="12"/>
+      <c r="S127" s="10"/>
+      <c r="T127" s="11"/>
+      <c r="U127" s="11"/>
+      <c r="V127" s="12"/>
+      <c r="W127" s="10"/>
+      <c r="X127" s="12"/>
+      <c r="Y127" s="10"/>
+      <c r="Z127" s="11"/>
+      <c r="AA127" s="11"/>
+      <c r="AB127" s="12"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>84</v>
@@ -6146,39 +6128,39 @@
       <c r="C128" s="5"/>
       <c r="D128" s="6"/>
       <c r="E128" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F128" s="5"/>
       <c r="G128" s="6"/>
       <c r="H128" s="2">
-        <v>3899</v>
+        <v>1899</v>
       </c>
       <c r="I128" s="6"/>
-      <c r="J128" s="16" t="s">
-        <v>127</v>
+      <c r="J128" s="13" t="s">
+        <v>126</v>
       </c>
       <c r="K128" s="5"/>
       <c r="L128" s="5"/>
       <c r="M128" s="5"/>
       <c r="N128" s="6"/>
       <c r="O128" s="2" t="s">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="P128" s="5"/>
       <c r="Q128" s="5"/>
       <c r="R128" s="6"/>
       <c r="S128" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T128" s="5"/>
       <c r="U128" s="5"/>
       <c r="V128" s="6"/>
       <c r="W128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X128" s="6"/>
-      <c r="Y128" s="17" t="s">
-        <v>256</v>
+      <c r="Y128" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="Z128" s="5"/>
       <c r="AA128" s="5"/>
@@ -6246,7 +6228,7 @@
     </row>
     <row r="131" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>85</v>
@@ -6259,18 +6241,18 @@
       <c r="F131" s="5"/>
       <c r="G131" s="6"/>
       <c r="H131" s="2">
-        <v>1899</v>
+        <v>1199</v>
       </c>
       <c r="I131" s="6"/>
-      <c r="J131" s="16" t="s">
-        <v>128</v>
+      <c r="J131" s="13" t="s">
+        <v>127</v>
       </c>
       <c r="K131" s="5"/>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
       <c r="N131" s="6"/>
       <c r="O131" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="P131" s="5"/>
       <c r="Q131" s="5"/>
@@ -6285,8 +6267,8 @@
         <v>0</v>
       </c>
       <c r="X131" s="6"/>
-      <c r="Y131" s="17" t="s">
-        <v>257</v>
+      <c r="Y131" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="Z131" s="5"/>
       <c r="AA131" s="5"/>
@@ -6354,7 +6336,7 @@
     </row>
     <row r="134" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>86</v>
@@ -6367,18 +6349,18 @@
       <c r="F134" s="5"/>
       <c r="G134" s="6"/>
       <c r="H134" s="2">
-        <v>1199</v>
+        <v>1999</v>
       </c>
       <c r="I134" s="6"/>
-      <c r="J134" s="16" t="s">
-        <v>129</v>
+      <c r="J134" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
       <c r="N134" s="6"/>
       <c r="O134" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="P134" s="5"/>
       <c r="Q134" s="5"/>
@@ -6393,8 +6375,8 @@
         <v>0</v>
       </c>
       <c r="X134" s="6"/>
-      <c r="Y134" s="17" t="s">
-        <v>258</v>
+      <c r="Y134" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="Z134" s="5"/>
       <c r="AA134" s="5"/>
@@ -6462,7 +6444,7 @@
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>87</v>
@@ -6470,39 +6452,39 @@
       <c r="C137" s="5"/>
       <c r="D137" s="6"/>
       <c r="E137" s="2" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="F137" s="5"/>
       <c r="G137" s="6"/>
       <c r="H137" s="2">
-        <v>1999</v>
+        <v>4499</v>
       </c>
       <c r="I137" s="6"/>
-      <c r="J137" s="16" t="s">
-        <v>130</v>
+      <c r="J137" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="K137" s="5"/>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
       <c r="N137" s="6"/>
       <c r="O137" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P137" s="5"/>
       <c r="Q137" s="5"/>
       <c r="R137" s="6"/>
       <c r="S137" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="T137" s="5"/>
       <c r="U137" s="5"/>
       <c r="V137" s="6"/>
       <c r="W137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X137" s="6"/>
-      <c r="Y137" s="17" t="s">
-        <v>259</v>
+      <c r="Y137" s="14" t="s">
+        <v>256</v>
       </c>
       <c r="Z137" s="5"/>
       <c r="AA137" s="5"/>
@@ -6570,47 +6552,47 @@
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C140" s="5"/>
       <c r="D140" s="6"/>
       <c r="E140" s="2" t="s">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="F140" s="5"/>
       <c r="G140" s="6"/>
       <c r="H140" s="2">
-        <v>4499</v>
+        <v>2499</v>
       </c>
       <c r="I140" s="6"/>
-      <c r="J140" s="16" t="s">
-        <v>131</v>
+      <c r="J140" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="K140" s="5"/>
       <c r="L140" s="5"/>
       <c r="M140" s="5"/>
       <c r="N140" s="6"/>
       <c r="O140" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P140" s="5"/>
       <c r="Q140" s="5"/>
       <c r="R140" s="6"/>
       <c r="S140" s="2" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="T140" s="5"/>
       <c r="U140" s="5"/>
       <c r="V140" s="6"/>
       <c r="W140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X140" s="6"/>
-      <c r="Y140" s="17" t="s">
-        <v>261</v>
+      <c r="Y140" s="14" t="s">
+        <v>257</v>
       </c>
       <c r="Z140" s="5"/>
       <c r="AA140" s="5"/>
@@ -6678,7 +6660,7 @@
     </row>
     <row r="143" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>90</v>
@@ -6686,39 +6668,39 @@
       <c r="C143" s="5"/>
       <c r="D143" s="6"/>
       <c r="E143" s="2" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="F143" s="5"/>
       <c r="G143" s="6"/>
       <c r="H143" s="2">
-        <v>2499</v>
+        <v>4299</v>
       </c>
       <c r="I143" s="6"/>
-      <c r="J143" s="16" t="s">
-        <v>132</v>
+      <c r="J143" s="13" t="s">
+        <v>131</v>
       </c>
       <c r="K143" s="5"/>
       <c r="L143" s="5"/>
       <c r="M143" s="5"/>
       <c r="N143" s="6"/>
       <c r="O143" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="P143" s="5"/>
       <c r="Q143" s="5"/>
       <c r="R143" s="6"/>
       <c r="S143" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="T143" s="5"/>
       <c r="U143" s="5"/>
       <c r="V143" s="6"/>
       <c r="W143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X143" s="6"/>
-      <c r="Y143" s="17" t="s">
-        <v>262</v>
+      <c r="Y143" s="14" t="s">
+        <v>258</v>
       </c>
       <c r="Z143" s="5"/>
       <c r="AA143" s="5"/>
@@ -6786,7 +6768,7 @@
     </row>
     <row r="146" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>91</v>
@@ -6794,29 +6776,29 @@
       <c r="C146" s="5"/>
       <c r="D146" s="6"/>
       <c r="E146" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F146" s="5"/>
       <c r="G146" s="6"/>
       <c r="H146" s="2">
-        <v>4299</v>
+        <v>2999</v>
       </c>
       <c r="I146" s="6"/>
-      <c r="J146" s="16" t="s">
-        <v>133</v>
+      <c r="J146" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="K146" s="5"/>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
       <c r="N146" s="6"/>
       <c r="O146" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P146" s="5"/>
       <c r="Q146" s="5"/>
       <c r="R146" s="6"/>
       <c r="S146" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="T146" s="5"/>
       <c r="U146" s="5"/>
@@ -6825,8 +6807,8 @@
         <v>1</v>
       </c>
       <c r="X146" s="6"/>
-      <c r="Y146" s="17" t="s">
-        <v>263</v>
+      <c r="Y146" s="14" t="s">
+        <v>259</v>
       </c>
       <c r="Z146" s="5"/>
       <c r="AA146" s="5"/>
@@ -6894,47 +6876,47 @@
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C149" s="5"/>
       <c r="D149" s="6"/>
       <c r="E149" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F149" s="5"/>
       <c r="G149" s="6"/>
       <c r="H149" s="2">
-        <v>2999</v>
+        <v>5299</v>
       </c>
       <c r="I149" s="6"/>
-      <c r="J149" s="16" t="s">
-        <v>134</v>
+      <c r="J149" s="13" t="s">
+        <v>133</v>
       </c>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="5"/>
       <c r="N149" s="6"/>
       <c r="O149" s="2" t="s">
-        <v>159</v>
+        <v>255</v>
       </c>
       <c r="P149" s="5"/>
       <c r="Q149" s="5"/>
       <c r="R149" s="6"/>
       <c r="S149" s="2" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="T149" s="5"/>
       <c r="U149" s="5"/>
       <c r="V149" s="6"/>
       <c r="W149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X149" s="6"/>
-      <c r="Y149" s="17" t="s">
-        <v>264</v>
+      <c r="Y149" s="14" t="s">
+        <v>260</v>
       </c>
       <c r="Z149" s="5"/>
       <c r="AA149" s="5"/>
@@ -7002,7 +6984,7 @@
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>94</v>
@@ -7010,29 +6992,29 @@
       <c r="C152" s="5"/>
       <c r="D152" s="6"/>
       <c r="E152" s="2" t="s">
-        <v>149</v>
+        <v>10</v>
       </c>
       <c r="F152" s="5"/>
       <c r="G152" s="6"/>
       <c r="H152" s="2">
-        <v>5299</v>
+        <v>3299</v>
       </c>
       <c r="I152" s="6"/>
-      <c r="J152" s="16" t="s">
-        <v>135</v>
+      <c r="J152" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
       <c r="N152" s="6"/>
       <c r="O152" s="2" t="s">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="P152" s="5"/>
       <c r="Q152" s="5"/>
       <c r="R152" s="6"/>
       <c r="S152" s="2" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="T152" s="5"/>
       <c r="U152" s="5"/>
@@ -7041,8 +7023,8 @@
         <v>0</v>
       </c>
       <c r="X152" s="6"/>
-      <c r="Y152" s="17" t="s">
-        <v>265</v>
+      <c r="Y152" s="14" t="s">
+        <v>261</v>
       </c>
       <c r="Z152" s="5"/>
       <c r="AA152" s="5"/>
@@ -7110,10 +7092,10 @@
     </row>
     <row r="155" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C155" s="5"/>
       <c r="D155" s="6"/>
@@ -7123,24 +7105,24 @@
       <c r="F155" s="5"/>
       <c r="G155" s="6"/>
       <c r="H155" s="2">
-        <v>3299</v>
+        <v>3399</v>
       </c>
       <c r="I155" s="6"/>
-      <c r="J155" s="16" t="s">
-        <v>136</v>
+      <c r="J155" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="K155" s="5"/>
       <c r="L155" s="5"/>
       <c r="M155" s="5"/>
       <c r="N155" s="6"/>
       <c r="O155" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P155" s="5"/>
       <c r="Q155" s="5"/>
       <c r="R155" s="6"/>
       <c r="S155" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T155" s="5"/>
       <c r="U155" s="5"/>
@@ -7149,8 +7131,8 @@
         <v>0</v>
       </c>
       <c r="X155" s="6"/>
-      <c r="Y155" s="17" t="s">
-        <v>266</v>
+      <c r="Y155" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="Z155" s="5"/>
       <c r="AA155" s="5"/>
@@ -7218,7 +7200,7 @@
     </row>
     <row r="158" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>97</v>
@@ -7231,24 +7213,24 @@
       <c r="F158" s="5"/>
       <c r="G158" s="6"/>
       <c r="H158" s="2">
-        <v>3399</v>
+        <v>4499</v>
       </c>
       <c r="I158" s="6"/>
-      <c r="J158" s="16" t="s">
-        <v>137</v>
+      <c r="J158" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="K158" s="5"/>
       <c r="L158" s="5"/>
       <c r="M158" s="5"/>
       <c r="N158" s="6"/>
       <c r="O158" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P158" s="5"/>
       <c r="Q158" s="5"/>
       <c r="R158" s="6"/>
       <c r="S158" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="T158" s="5"/>
       <c r="U158" s="5"/>
@@ -7257,8 +7239,8 @@
         <v>0</v>
       </c>
       <c r="X158" s="6"/>
-      <c r="Y158" s="17" t="s">
-        <v>267</v>
+      <c r="Y158" s="14" t="s">
+        <v>263</v>
       </c>
       <c r="Z158" s="5"/>
       <c r="AA158" s="5"/>
@@ -7326,10 +7308,10 @@
     </row>
     <row r="161" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C161" s="5"/>
       <c r="D161" s="6"/>
@@ -7339,24 +7321,24 @@
       <c r="F161" s="5"/>
       <c r="G161" s="6"/>
       <c r="H161" s="2">
-        <v>4499</v>
+        <v>3299</v>
       </c>
       <c r="I161" s="6"/>
-      <c r="J161" s="16" t="s">
-        <v>138</v>
+      <c r="J161" s="13" t="s">
+        <v>137</v>
       </c>
       <c r="K161" s="5"/>
       <c r="L161" s="5"/>
       <c r="M161" s="5"/>
       <c r="N161" s="6"/>
       <c r="O161" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="P161" s="5"/>
       <c r="Q161" s="5"/>
       <c r="R161" s="6"/>
       <c r="S161" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="T161" s="5"/>
       <c r="U161" s="5"/>
@@ -7365,8 +7347,8 @@
         <v>0</v>
       </c>
       <c r="X161" s="6"/>
-      <c r="Y161" s="17" t="s">
-        <v>268</v>
+      <c r="Y161" s="14" t="s">
+        <v>265</v>
       </c>
       <c r="Z161" s="5"/>
       <c r="AA161" s="5"/>
@@ -7434,7 +7416,7 @@
     </row>
     <row r="164" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>100</v>
@@ -7447,24 +7429,24 @@
       <c r="F164" s="5"/>
       <c r="G164" s="6"/>
       <c r="H164" s="2">
-        <v>3299</v>
+        <v>3499</v>
       </c>
       <c r="I164" s="6"/>
-      <c r="J164" s="16" t="s">
-        <v>139</v>
+      <c r="J164" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="K164" s="5"/>
       <c r="L164" s="5"/>
       <c r="M164" s="5"/>
       <c r="N164" s="6"/>
       <c r="O164" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P164" s="5"/>
       <c r="Q164" s="5"/>
       <c r="R164" s="6"/>
       <c r="S164" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T164" s="5"/>
       <c r="U164" s="5"/>
@@ -7473,8 +7455,8 @@
         <v>0</v>
       </c>
       <c r="X164" s="6"/>
-      <c r="Y164" s="17" t="s">
-        <v>270</v>
+      <c r="Y164" s="14" t="s">
+        <v>264</v>
       </c>
       <c r="Z164" s="5"/>
       <c r="AA164" s="5"/>
@@ -7542,7 +7524,7 @@
     </row>
     <row r="167" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>101</v>
@@ -7550,39 +7532,39 @@
       <c r="C167" s="5"/>
       <c r="D167" s="6"/>
       <c r="E167" s="2" t="s">
-        <v>10</v>
+        <v>148</v>
       </c>
       <c r="F167" s="5"/>
       <c r="G167" s="6"/>
       <c r="H167" s="2">
-        <v>3499</v>
+        <v>4999</v>
       </c>
       <c r="I167" s="6"/>
-      <c r="J167" s="16" t="s">
-        <v>140</v>
+      <c r="J167" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="K167" s="5"/>
       <c r="L167" s="5"/>
       <c r="M167" s="5"/>
       <c r="N167" s="6"/>
       <c r="O167" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P167" s="5"/>
       <c r="Q167" s="5"/>
       <c r="R167" s="6"/>
       <c r="S167" s="2" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="T167" s="5"/>
       <c r="U167" s="5"/>
       <c r="V167" s="6"/>
       <c r="W167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X167" s="6"/>
-      <c r="Y167" s="17" t="s">
-        <v>269</v>
+      <c r="Y167" s="14" t="s">
+        <v>267</v>
       </c>
       <c r="Z167" s="5"/>
       <c r="AA167" s="5"/>
@@ -7650,7 +7632,7 @@
     </row>
     <row r="170" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>102</v>
@@ -7658,29 +7640,29 @@
       <c r="C170" s="5"/>
       <c r="D170" s="6"/>
       <c r="E170" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F170" s="5"/>
       <c r="G170" s="6"/>
       <c r="H170" s="2">
-        <v>4999</v>
+        <v>8999</v>
       </c>
       <c r="I170" s="6"/>
-      <c r="J170" s="16" t="s">
-        <v>141</v>
+      <c r="J170" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="K170" s="5"/>
       <c r="L170" s="5"/>
       <c r="M170" s="5"/>
       <c r="N170" s="6"/>
       <c r="O170" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P170" s="5"/>
       <c r="Q170" s="5"/>
       <c r="R170" s="6"/>
       <c r="S170" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T170" s="5"/>
       <c r="U170" s="5"/>
@@ -7689,8 +7671,8 @@
         <v>1</v>
       </c>
       <c r="X170" s="6"/>
-      <c r="Y170" s="17" t="s">
-        <v>272</v>
+      <c r="Y170" s="14" t="s">
+        <v>266</v>
       </c>
       <c r="Z170" s="5"/>
       <c r="AA170" s="5"/>
@@ -7758,37 +7740,37 @@
     </row>
     <row r="173" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C173" s="5"/>
       <c r="D173" s="6"/>
       <c r="E173" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F173" s="5"/>
       <c r="G173" s="6"/>
       <c r="H173" s="2">
-        <v>8999</v>
+        <v>5499</v>
       </c>
       <c r="I173" s="6"/>
-      <c r="J173" s="16" t="s">
-        <v>142</v>
+      <c r="J173" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="K173" s="5"/>
       <c r="L173" s="5"/>
       <c r="M173" s="5"/>
       <c r="N173" s="6"/>
       <c r="O173" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P173" s="5"/>
       <c r="Q173" s="5"/>
       <c r="R173" s="6"/>
       <c r="S173" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T173" s="5"/>
       <c r="U173" s="5"/>
@@ -7797,8 +7779,8 @@
         <v>1</v>
       </c>
       <c r="X173" s="6"/>
-      <c r="Y173" s="17" t="s">
-        <v>271</v>
+      <c r="Y173" s="14" t="s">
+        <v>268</v>
       </c>
       <c r="Z173" s="5"/>
       <c r="AA173" s="5"/>
@@ -7866,577 +7848,577 @@
     </row>
     <row r="176" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C176" s="5"/>
-      <c r="D176" s="6"/>
+        <v>63</v>
+      </c>
+      <c r="C176" s="15"/>
+      <c r="D176" s="15"/>
       <c r="E176" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F176" s="5"/>
-      <c r="G176" s="6"/>
+        <v>29</v>
+      </c>
+      <c r="F176" s="15"/>
+      <c r="G176" s="15"/>
       <c r="H176" s="2">
-        <v>5499</v>
-      </c>
-      <c r="I176" s="6"/>
-      <c r="J176" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="K176" s="5"/>
-      <c r="L176" s="5"/>
-      <c r="M176" s="5"/>
-      <c r="N176" s="6"/>
+        <v>1299</v>
+      </c>
+      <c r="I176" s="15"/>
+      <c r="J176" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="K176" s="15"/>
+      <c r="L176" s="15"/>
+      <c r="M176" s="15"/>
+      <c r="N176" s="15"/>
       <c r="O176" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="P176" s="5"/>
-      <c r="Q176" s="5"/>
-      <c r="R176" s="6"/>
+        <v>146</v>
+      </c>
+      <c r="P176" s="15"/>
+      <c r="Q176" s="15"/>
+      <c r="R176" s="15"/>
       <c r="S176" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="T176" s="5"/>
-      <c r="U176" s="5"/>
-      <c r="V176" s="6"/>
+        <v>41</v>
+      </c>
+      <c r="T176" s="15"/>
+      <c r="U176" s="15"/>
+      <c r="V176" s="15"/>
       <c r="W176" s="2">
-        <v>1</v>
-      </c>
-      <c r="X176" s="6"/>
-      <c r="Y176" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="Z176" s="5"/>
-      <c r="AA176" s="5"/>
-      <c r="AB176" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="X176" s="15"/>
+      <c r="Y176" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z176" s="15"/>
+      <c r="AA176" s="15"/>
+      <c r="AB176" s="15"/>
     </row>
     <row r="177" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A177" s="3"/>
-      <c r="B177" s="7"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="9"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="9"/>
-      <c r="H177" s="7"/>
-      <c r="I177" s="9"/>
-      <c r="J177" s="7"/>
-      <c r="K177" s="8"/>
-      <c r="L177" s="8"/>
-      <c r="M177" s="8"/>
-      <c r="N177" s="9"/>
-      <c r="O177" s="7"/>
-      <c r="P177" s="8"/>
-      <c r="Q177" s="8"/>
-      <c r="R177" s="9"/>
-      <c r="S177" s="7"/>
-      <c r="T177" s="8"/>
-      <c r="U177" s="8"/>
-      <c r="V177" s="9"/>
-      <c r="W177" s="7"/>
-      <c r="X177" s="9"/>
-      <c r="Y177" s="7"/>
-      <c r="Z177" s="8"/>
-      <c r="AA177" s="8"/>
-      <c r="AB177" s="9"/>
+      <c r="A177" s="15"/>
+      <c r="B177" s="15"/>
+      <c r="C177" s="15"/>
+      <c r="D177" s="15"/>
+      <c r="E177" s="15"/>
+      <c r="F177" s="15"/>
+      <c r="G177" s="15"/>
+      <c r="H177" s="15"/>
+      <c r="I177" s="15"/>
+      <c r="J177" s="15"/>
+      <c r="K177" s="15"/>
+      <c r="L177" s="15"/>
+      <c r="M177" s="15"/>
+      <c r="N177" s="15"/>
+      <c r="O177" s="15"/>
+      <c r="P177" s="15"/>
+      <c r="Q177" s="15"/>
+      <c r="R177" s="15"/>
+      <c r="S177" s="15"/>
+      <c r="T177" s="15"/>
+      <c r="U177" s="15"/>
+      <c r="V177" s="15"/>
+      <c r="W177" s="15"/>
+      <c r="X177" s="15"/>
+      <c r="Y177" s="15"/>
+      <c r="Z177" s="15"/>
+      <c r="AA177" s="15"/>
+      <c r="AB177" s="15"/>
     </row>
     <row r="178" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A178" s="4"/>
-      <c r="B178" s="10"/>
-      <c r="C178" s="11"/>
-      <c r="D178" s="12"/>
-      <c r="E178" s="10"/>
-      <c r="F178" s="11"/>
-      <c r="G178" s="12"/>
-      <c r="H178" s="10"/>
-      <c r="I178" s="12"/>
-      <c r="J178" s="10"/>
-      <c r="K178" s="11"/>
-      <c r="L178" s="11"/>
-      <c r="M178" s="11"/>
-      <c r="N178" s="12"/>
-      <c r="O178" s="10"/>
-      <c r="P178" s="11"/>
-      <c r="Q178" s="11"/>
-      <c r="R178" s="12"/>
-      <c r="S178" s="10"/>
-      <c r="T178" s="11"/>
-      <c r="U178" s="11"/>
-      <c r="V178" s="12"/>
-      <c r="W178" s="10"/>
-      <c r="X178" s="12"/>
-      <c r="Y178" s="10"/>
-      <c r="Z178" s="11"/>
-      <c r="AA178" s="11"/>
-      <c r="AB178" s="12"/>
+      <c r="A178" s="15"/>
+      <c r="B178" s="15"/>
+      <c r="C178" s="15"/>
+      <c r="D178" s="15"/>
+      <c r="E178" s="15"/>
+      <c r="F178" s="15"/>
+      <c r="G178" s="15"/>
+      <c r="H178" s="15"/>
+      <c r="I178" s="15"/>
+      <c r="J178" s="15"/>
+      <c r="K178" s="15"/>
+      <c r="L178" s="15"/>
+      <c r="M178" s="15"/>
+      <c r="N178" s="15"/>
+      <c r="O178" s="15"/>
+      <c r="P178" s="15"/>
+      <c r="Q178" s="15"/>
+      <c r="R178" s="15"/>
+      <c r="S178" s="15"/>
+      <c r="T178" s="15"/>
+      <c r="U178" s="15"/>
+      <c r="V178" s="15"/>
+      <c r="W178" s="15"/>
+      <c r="X178" s="15"/>
+      <c r="Y178" s="15"/>
+      <c r="Z178" s="15"/>
+      <c r="AA178" s="15"/>
+      <c r="AB178" s="15"/>
     </row>
     <row r="179" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C179" s="60"/>
-      <c r="D179" s="60"/>
+        <v>173</v>
+      </c>
+      <c r="C179" s="15"/>
+      <c r="D179" s="15"/>
       <c r="E179" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F179" s="60"/>
-      <c r="G179" s="60"/>
+        <v>177</v>
+      </c>
+      <c r="F179" s="15"/>
+      <c r="G179" s="15"/>
       <c r="H179" s="2">
-        <v>1299</v>
-      </c>
-      <c r="I179" s="60"/>
-      <c r="J179" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="K179" s="60"/>
-      <c r="L179" s="60"/>
-      <c r="M179" s="60"/>
-      <c r="N179" s="60"/>
+        <v>2699</v>
+      </c>
+      <c r="I179" s="15"/>
+      <c r="J179" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="K179" s="15"/>
+      <c r="L179" s="15"/>
+      <c r="M179" s="15"/>
+      <c r="N179" s="15"/>
       <c r="O179" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="P179" s="60"/>
-      <c r="Q179" s="60"/>
-      <c r="R179" s="60"/>
+        <v>174</v>
+      </c>
+      <c r="P179" s="15"/>
+      <c r="Q179" s="15"/>
+      <c r="R179" s="15"/>
       <c r="S179" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T179" s="60"/>
-      <c r="U179" s="60"/>
-      <c r="V179" s="60"/>
+        <v>176</v>
+      </c>
+      <c r="T179" s="15"/>
+      <c r="U179" s="15"/>
+      <c r="V179" s="15"/>
       <c r="W179" s="2">
-        <v>0</v>
-      </c>
-      <c r="X179" s="60"/>
-      <c r="Y179" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z179" s="60"/>
-      <c r="AA179" s="60"/>
-      <c r="AB179" s="60"/>
+        <v>1</v>
+      </c>
+      <c r="X179" s="15"/>
+      <c r="Y179" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z179" s="15"/>
+      <c r="AA179" s="15"/>
+      <c r="AB179" s="15"/>
     </row>
     <row r="180" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A180" s="60"/>
-      <c r="B180" s="60"/>
-      <c r="C180" s="60"/>
-      <c r="D180" s="60"/>
-      <c r="E180" s="60"/>
-      <c r="F180" s="60"/>
-      <c r="G180" s="60"/>
-      <c r="H180" s="60"/>
-      <c r="I180" s="60"/>
-      <c r="J180" s="60"/>
-      <c r="K180" s="60"/>
-      <c r="L180" s="60"/>
-      <c r="M180" s="60"/>
-      <c r="N180" s="60"/>
-      <c r="O180" s="60"/>
-      <c r="P180" s="60"/>
-      <c r="Q180" s="60"/>
-      <c r="R180" s="60"/>
-      <c r="S180" s="60"/>
-      <c r="T180" s="60"/>
-      <c r="U180" s="60"/>
-      <c r="V180" s="60"/>
-      <c r="W180" s="60"/>
-      <c r="X180" s="60"/>
-      <c r="Y180" s="60"/>
-      <c r="Z180" s="60"/>
-      <c r="AA180" s="60"/>
-      <c r="AB180" s="60"/>
+      <c r="A180" s="15"/>
+      <c r="B180" s="15"/>
+      <c r="C180" s="15"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="15"/>
+      <c r="F180" s="15"/>
+      <c r="G180" s="15"/>
+      <c r="H180" s="15"/>
+      <c r="I180" s="15"/>
+      <c r="J180" s="15"/>
+      <c r="K180" s="15"/>
+      <c r="L180" s="15"/>
+      <c r="M180" s="15"/>
+      <c r="N180" s="15"/>
+      <c r="O180" s="15"/>
+      <c r="P180" s="15"/>
+      <c r="Q180" s="15"/>
+      <c r="R180" s="15"/>
+      <c r="S180" s="15"/>
+      <c r="T180" s="15"/>
+      <c r="U180" s="15"/>
+      <c r="V180" s="15"/>
+      <c r="W180" s="15"/>
+      <c r="X180" s="15"/>
+      <c r="Y180" s="15"/>
+      <c r="Z180" s="15"/>
+      <c r="AA180" s="15"/>
+      <c r="AB180" s="15"/>
     </row>
     <row r="181" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A181" s="60"/>
-      <c r="B181" s="60"/>
-      <c r="C181" s="60"/>
-      <c r="D181" s="60"/>
-      <c r="E181" s="60"/>
-      <c r="F181" s="60"/>
-      <c r="G181" s="60"/>
-      <c r="H181" s="60"/>
-      <c r="I181" s="60"/>
-      <c r="J181" s="60"/>
-      <c r="K181" s="60"/>
-      <c r="L181" s="60"/>
-      <c r="M181" s="60"/>
-      <c r="N181" s="60"/>
-      <c r="O181" s="60"/>
-      <c r="P181" s="60"/>
-      <c r="Q181" s="60"/>
-      <c r="R181" s="60"/>
-      <c r="S181" s="60"/>
-      <c r="T181" s="60"/>
-      <c r="U181" s="60"/>
-      <c r="V181" s="60"/>
-      <c r="W181" s="60"/>
-      <c r="X181" s="60"/>
-      <c r="Y181" s="60"/>
-      <c r="Z181" s="60"/>
-      <c r="AA181" s="60"/>
-      <c r="AB181" s="60"/>
+      <c r="A181" s="15"/>
+      <c r="B181" s="15"/>
+      <c r="C181" s="15"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="15"/>
+      <c r="F181" s="15"/>
+      <c r="G181" s="15"/>
+      <c r="H181" s="15"/>
+      <c r="I181" s="15"/>
+      <c r="J181" s="15"/>
+      <c r="K181" s="15"/>
+      <c r="L181" s="15"/>
+      <c r="M181" s="15"/>
+      <c r="N181" s="15"/>
+      <c r="O181" s="15"/>
+      <c r="P181" s="15"/>
+      <c r="Q181" s="15"/>
+      <c r="R181" s="15"/>
+      <c r="S181" s="15"/>
+      <c r="T181" s="15"/>
+      <c r="U181" s="15"/>
+      <c r="V181" s="15"/>
+      <c r="W181" s="15"/>
+      <c r="X181" s="15"/>
+      <c r="Y181" s="15"/>
+      <c r="Z181" s="15"/>
+      <c r="AA181" s="15"/>
+      <c r="AB181" s="15"/>
     </row>
     <row r="182" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C182" s="60"/>
-      <c r="D182" s="60"/>
+        <v>25</v>
+      </c>
+      <c r="C182" s="5"/>
+      <c r="D182" s="6"/>
       <c r="E182" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F182" s="60"/>
-      <c r="G182" s="60"/>
+      <c r="F182" s="5"/>
+      <c r="G182" s="6"/>
       <c r="H182" s="2">
-        <v>2699</v>
-      </c>
-      <c r="I182" s="60"/>
-      <c r="J182" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="K182" s="60"/>
-      <c r="L182" s="60"/>
-      <c r="M182" s="60"/>
-      <c r="N182" s="60"/>
+        <v>1599</v>
+      </c>
+      <c r="I182" s="6"/>
+      <c r="J182" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K182" s="5"/>
+      <c r="L182" s="5"/>
+      <c r="M182" s="5"/>
+      <c r="N182" s="6"/>
       <c r="O182" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="P182" s="60"/>
-      <c r="Q182" s="60"/>
-      <c r="R182" s="60"/>
+        <v>183</v>
+      </c>
+      <c r="P182" s="5"/>
+      <c r="Q182" s="5"/>
+      <c r="R182" s="6"/>
       <c r="S182" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="T182" s="60"/>
-      <c r="U182" s="60"/>
-      <c r="V182" s="60"/>
+        <v>24</v>
+      </c>
+      <c r="T182" s="5"/>
+      <c r="U182" s="5"/>
+      <c r="V182" s="6"/>
       <c r="W182" s="2">
-        <v>1</v>
-      </c>
-      <c r="X182" s="60"/>
-      <c r="Y182" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z182" s="60"/>
-      <c r="AA182" s="60"/>
-      <c r="AB182" s="60"/>
+        <v>0</v>
+      </c>
+      <c r="X182" s="6"/>
+      <c r="Y182" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z182" s="5"/>
+      <c r="AA182" s="5"/>
+      <c r="AB182" s="6"/>
     </row>
     <row r="183" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A183" s="60"/>
-      <c r="B183" s="60"/>
-      <c r="C183" s="60"/>
-      <c r="D183" s="60"/>
-      <c r="E183" s="60"/>
-      <c r="F183" s="60"/>
-      <c r="G183" s="60"/>
-      <c r="H183" s="60"/>
-      <c r="I183" s="60"/>
-      <c r="J183" s="60"/>
-      <c r="K183" s="60"/>
-      <c r="L183" s="60"/>
-      <c r="M183" s="60"/>
-      <c r="N183" s="60"/>
-      <c r="O183" s="60"/>
-      <c r="P183" s="60"/>
-      <c r="Q183" s="60"/>
-      <c r="R183" s="60"/>
-      <c r="S183" s="60"/>
-      <c r="T183" s="60"/>
-      <c r="U183" s="60"/>
-      <c r="V183" s="60"/>
-      <c r="W183" s="60"/>
-      <c r="X183" s="60"/>
-      <c r="Y183" s="60"/>
-      <c r="Z183" s="60"/>
-      <c r="AA183" s="60"/>
-      <c r="AB183" s="60"/>
+      <c r="A183" s="3"/>
+      <c r="B183" s="7"/>
+      <c r="C183" s="8"/>
+      <c r="D183" s="9"/>
+      <c r="E183" s="7"/>
+      <c r="F183" s="8"/>
+      <c r="G183" s="9"/>
+      <c r="H183" s="7"/>
+      <c r="I183" s="9"/>
+      <c r="J183" s="7"/>
+      <c r="K183" s="8"/>
+      <c r="L183" s="8"/>
+      <c r="M183" s="8"/>
+      <c r="N183" s="9"/>
+      <c r="O183" s="7"/>
+      <c r="P183" s="8"/>
+      <c r="Q183" s="8"/>
+      <c r="R183" s="9"/>
+      <c r="S183" s="7"/>
+      <c r="T183" s="8"/>
+      <c r="U183" s="8"/>
+      <c r="V183" s="9"/>
+      <c r="W183" s="7"/>
+      <c r="X183" s="9"/>
+      <c r="Y183" s="7"/>
+      <c r="Z183" s="8"/>
+      <c r="AA183" s="8"/>
+      <c r="AB183" s="9"/>
     </row>
     <row r="184" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A184" s="60"/>
-      <c r="B184" s="60"/>
-      <c r="C184" s="60"/>
-      <c r="D184" s="60"/>
-      <c r="E184" s="60"/>
-      <c r="F184" s="60"/>
-      <c r="G184" s="60"/>
-      <c r="H184" s="60"/>
-      <c r="I184" s="60"/>
-      <c r="J184" s="60"/>
-      <c r="K184" s="60"/>
-      <c r="L184" s="60"/>
-      <c r="M184" s="60"/>
-      <c r="N184" s="60"/>
-      <c r="O184" s="60"/>
-      <c r="P184" s="60"/>
-      <c r="Q184" s="60"/>
-      <c r="R184" s="60"/>
-      <c r="S184" s="60"/>
-      <c r="T184" s="60"/>
-      <c r="U184" s="60"/>
-      <c r="V184" s="60"/>
-      <c r="W184" s="60"/>
-      <c r="X184" s="60"/>
-      <c r="Y184" s="60"/>
-      <c r="Z184" s="60"/>
-      <c r="AA184" s="60"/>
-      <c r="AB184" s="60"/>
+      <c r="A184" s="4"/>
+      <c r="B184" s="10"/>
+      <c r="C184" s="11"/>
+      <c r="D184" s="12"/>
+      <c r="E184" s="10"/>
+      <c r="F184" s="11"/>
+      <c r="G184" s="12"/>
+      <c r="H184" s="10"/>
+      <c r="I184" s="12"/>
+      <c r="J184" s="10"/>
+      <c r="K184" s="11"/>
+      <c r="L184" s="11"/>
+      <c r="M184" s="11"/>
+      <c r="N184" s="12"/>
+      <c r="O184" s="10"/>
+      <c r="P184" s="11"/>
+      <c r="Q184" s="11"/>
+      <c r="R184" s="12"/>
+      <c r="S184" s="10"/>
+      <c r="T184" s="11"/>
+      <c r="U184" s="11"/>
+      <c r="V184" s="12"/>
+      <c r="W184" s="10"/>
+      <c r="X184" s="12"/>
+      <c r="Y184" s="10"/>
+      <c r="Z184" s="11"/>
+      <c r="AA184" s="11"/>
+      <c r="AB184" s="12"/>
     </row>
     <row r="185" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C185" s="5"/>
-      <c r="D185" s="6"/>
+        <v>202</v>
+      </c>
+      <c r="C185" s="15"/>
+      <c r="D185" s="15"/>
       <c r="E185" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F185" s="5"/>
-      <c r="G185" s="6"/>
+        <v>147</v>
+      </c>
+      <c r="F185" s="15"/>
+      <c r="G185" s="15"/>
       <c r="H185" s="2">
-        <v>1599</v>
-      </c>
-      <c r="I185" s="6"/>
-      <c r="J185" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K185" s="5"/>
-      <c r="L185" s="5"/>
-      <c r="M185" s="5"/>
-      <c r="N185" s="6"/>
+        <v>4999</v>
+      </c>
+      <c r="I185" s="15"/>
+      <c r="J185" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="K185" s="15"/>
+      <c r="L185" s="15"/>
+      <c r="M185" s="15"/>
+      <c r="N185" s="15"/>
       <c r="O185" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="P185" s="5"/>
-      <c r="Q185" s="5"/>
-      <c r="R185" s="6"/>
+        <v>275</v>
+      </c>
+      <c r="P185" s="15"/>
+      <c r="Q185" s="15"/>
+      <c r="R185" s="15"/>
       <c r="S185" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T185" s="5"/>
-      <c r="U185" s="5"/>
-      <c r="V185" s="6"/>
+        <v>270</v>
+      </c>
+      <c r="T185" s="15"/>
+      <c r="U185" s="15"/>
+      <c r="V185" s="15"/>
       <c r="W185" s="2">
-        <v>0</v>
-      </c>
-      <c r="X185" s="6"/>
-      <c r="Y185" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z185" s="5"/>
-      <c r="AA185" s="5"/>
-      <c r="AB185" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="X185" s="15"/>
+      <c r="Y185" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z185" s="15"/>
+      <c r="AA185" s="15"/>
+      <c r="AB185" s="15"/>
     </row>
     <row r="186" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A186" s="3"/>
-      <c r="B186" s="7"/>
-      <c r="C186" s="8"/>
-      <c r="D186" s="9"/>
-      <c r="E186" s="7"/>
-      <c r="F186" s="8"/>
-      <c r="G186" s="9"/>
-      <c r="H186" s="7"/>
-      <c r="I186" s="9"/>
-      <c r="J186" s="7"/>
-      <c r="K186" s="8"/>
-      <c r="L186" s="8"/>
-      <c r="M186" s="8"/>
-      <c r="N186" s="9"/>
-      <c r="O186" s="7"/>
-      <c r="P186" s="8"/>
-      <c r="Q186" s="8"/>
-      <c r="R186" s="9"/>
-      <c r="S186" s="7"/>
-      <c r="T186" s="8"/>
-      <c r="U186" s="8"/>
-      <c r="V186" s="9"/>
-      <c r="W186" s="7"/>
-      <c r="X186" s="9"/>
-      <c r="Y186" s="7"/>
-      <c r="Z186" s="8"/>
-      <c r="AA186" s="8"/>
-      <c r="AB186" s="9"/>
+      <c r="A186" s="15"/>
+      <c r="B186" s="15"/>
+      <c r="C186" s="15"/>
+      <c r="D186" s="15"/>
+      <c r="E186" s="15"/>
+      <c r="F186" s="15"/>
+      <c r="G186" s="15"/>
+      <c r="H186" s="15"/>
+      <c r="I186" s="15"/>
+      <c r="J186" s="15"/>
+      <c r="K186" s="15"/>
+      <c r="L186" s="15"/>
+      <c r="M186" s="15"/>
+      <c r="N186" s="15"/>
+      <c r="O186" s="15"/>
+      <c r="P186" s="15"/>
+      <c r="Q186" s="15"/>
+      <c r="R186" s="15"/>
+      <c r="S186" s="15"/>
+      <c r="T186" s="15"/>
+      <c r="U186" s="15"/>
+      <c r="V186" s="15"/>
+      <c r="W186" s="15"/>
+      <c r="X186" s="15"/>
+      <c r="Y186" s="15"/>
+      <c r="Z186" s="15"/>
+      <c r="AA186" s="15"/>
+      <c r="AB186" s="15"/>
     </row>
     <row r="187" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A187" s="4"/>
-      <c r="B187" s="10"/>
-      <c r="C187" s="11"/>
-      <c r="D187" s="12"/>
-      <c r="E187" s="10"/>
-      <c r="F187" s="11"/>
-      <c r="G187" s="12"/>
-      <c r="H187" s="10"/>
-      <c r="I187" s="12"/>
-      <c r="J187" s="10"/>
-      <c r="K187" s="11"/>
-      <c r="L187" s="11"/>
-      <c r="M187" s="11"/>
-      <c r="N187" s="12"/>
-      <c r="O187" s="10"/>
-      <c r="P187" s="11"/>
-      <c r="Q187" s="11"/>
-      <c r="R187" s="12"/>
-      <c r="S187" s="10"/>
-      <c r="T187" s="11"/>
-      <c r="U187" s="11"/>
-      <c r="V187" s="12"/>
-      <c r="W187" s="10"/>
-      <c r="X187" s="12"/>
-      <c r="Y187" s="10"/>
-      <c r="Z187" s="11"/>
-      <c r="AA187" s="11"/>
-      <c r="AB187" s="12"/>
+      <c r="A187" s="15"/>
+      <c r="B187" s="15"/>
+      <c r="C187" s="15"/>
+      <c r="D187" s="15"/>
+      <c r="E187" s="15"/>
+      <c r="F187" s="15"/>
+      <c r="G187" s="15"/>
+      <c r="H187" s="15"/>
+      <c r="I187" s="15"/>
+      <c r="J187" s="15"/>
+      <c r="K187" s="15"/>
+      <c r="L187" s="15"/>
+      <c r="M187" s="15"/>
+      <c r="N187" s="15"/>
+      <c r="O187" s="15"/>
+      <c r="P187" s="15"/>
+      <c r="Q187" s="15"/>
+      <c r="R187" s="15"/>
+      <c r="S187" s="15"/>
+      <c r="T187" s="15"/>
+      <c r="U187" s="15"/>
+      <c r="V187" s="15"/>
+      <c r="W187" s="15"/>
+      <c r="X187" s="15"/>
+      <c r="Y187" s="15"/>
+      <c r="Z187" s="15"/>
+      <c r="AA187" s="15"/>
+      <c r="AB187" s="15"/>
     </row>
     <row r="188" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C188" s="60"/>
-      <c r="D188" s="60"/>
+        <v>21</v>
+      </c>
+      <c r="C188" s="5"/>
+      <c r="D188" s="6"/>
       <c r="E188" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F188" s="60"/>
-      <c r="G188" s="60"/>
+        <v>179</v>
+      </c>
+      <c r="F188" s="5"/>
+      <c r="G188" s="6"/>
       <c r="H188" s="2">
-        <v>4999</v>
-      </c>
-      <c r="I188" s="60"/>
-      <c r="J188" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="K188" s="60"/>
-      <c r="L188" s="60"/>
-      <c r="M188" s="60"/>
-      <c r="N188" s="60"/>
+        <v>1799</v>
+      </c>
+      <c r="I188" s="6"/>
+      <c r="J188" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="K188" s="5"/>
+      <c r="L188" s="5"/>
+      <c r="M188" s="5"/>
+      <c r="N188" s="6"/>
       <c r="O188" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="P188" s="60"/>
-      <c r="Q188" s="60"/>
-      <c r="R188" s="60"/>
+        <v>182</v>
+      </c>
+      <c r="P188" s="5"/>
+      <c r="Q188" s="5"/>
+      <c r="R188" s="6"/>
       <c r="S188" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="T188" s="60"/>
-      <c r="U188" s="60"/>
-      <c r="V188" s="60"/>
+        <v>24</v>
+      </c>
+      <c r="T188" s="5"/>
+      <c r="U188" s="5"/>
+      <c r="V188" s="6"/>
       <c r="W188" s="2">
-        <v>1</v>
-      </c>
-      <c r="X188" s="60"/>
-      <c r="Y188" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="Z188" s="60"/>
-      <c r="AA188" s="60"/>
-      <c r="AB188" s="60"/>
+        <v>0</v>
+      </c>
+      <c r="X188" s="6"/>
+      <c r="Y188" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z188" s="5"/>
+      <c r="AA188" s="5"/>
+      <c r="AB188" s="6"/>
     </row>
     <row r="189" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A189" s="60"/>
-      <c r="B189" s="60"/>
-      <c r="C189" s="60"/>
-      <c r="D189" s="60"/>
-      <c r="E189" s="60"/>
-      <c r="F189" s="60"/>
-      <c r="G189" s="60"/>
-      <c r="H189" s="60"/>
-      <c r="I189" s="60"/>
-      <c r="J189" s="60"/>
-      <c r="K189" s="60"/>
-      <c r="L189" s="60"/>
-      <c r="M189" s="60"/>
-      <c r="N189" s="60"/>
-      <c r="O189" s="60"/>
-      <c r="P189" s="60"/>
-      <c r="Q189" s="60"/>
-      <c r="R189" s="60"/>
-      <c r="S189" s="60"/>
-      <c r="T189" s="60"/>
-      <c r="U189" s="60"/>
-      <c r="V189" s="60"/>
-      <c r="W189" s="60"/>
-      <c r="X189" s="60"/>
-      <c r="Y189" s="60"/>
-      <c r="Z189" s="60"/>
-      <c r="AA189" s="60"/>
-      <c r="AB189" s="60"/>
+      <c r="A189" s="3"/>
+      <c r="B189" s="7"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="8"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="7"/>
+      <c r="I189" s="9"/>
+      <c r="J189" s="7"/>
+      <c r="K189" s="8"/>
+      <c r="L189" s="8"/>
+      <c r="M189" s="8"/>
+      <c r="N189" s="9"/>
+      <c r="O189" s="7"/>
+      <c r="P189" s="8"/>
+      <c r="Q189" s="8"/>
+      <c r="R189" s="9"/>
+      <c r="S189" s="7"/>
+      <c r="T189" s="8"/>
+      <c r="U189" s="8"/>
+      <c r="V189" s="9"/>
+      <c r="W189" s="7"/>
+      <c r="X189" s="9"/>
+      <c r="Y189" s="7"/>
+      <c r="Z189" s="8"/>
+      <c r="AA189" s="8"/>
+      <c r="AB189" s="9"/>
     </row>
     <row r="190" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A190" s="60"/>
-      <c r="B190" s="60"/>
-      <c r="C190" s="60"/>
-      <c r="D190" s="60"/>
-      <c r="E190" s="60"/>
-      <c r="F190" s="60"/>
-      <c r="G190" s="60"/>
-      <c r="H190" s="60"/>
-      <c r="I190" s="60"/>
-      <c r="J190" s="60"/>
-      <c r="K190" s="60"/>
-      <c r="L190" s="60"/>
-      <c r="M190" s="60"/>
-      <c r="N190" s="60"/>
-      <c r="O190" s="60"/>
-      <c r="P190" s="60"/>
-      <c r="Q190" s="60"/>
-      <c r="R190" s="60"/>
-      <c r="S190" s="60"/>
-      <c r="T190" s="60"/>
-      <c r="U190" s="60"/>
-      <c r="V190" s="60"/>
-      <c r="W190" s="60"/>
-      <c r="X190" s="60"/>
-      <c r="Y190" s="60"/>
-      <c r="Z190" s="60"/>
-      <c r="AA190" s="60"/>
-      <c r="AB190" s="60"/>
+      <c r="A190" s="4"/>
+      <c r="B190" s="10"/>
+      <c r="C190" s="11"/>
+      <c r="D190" s="12"/>
+      <c r="E190" s="10"/>
+      <c r="F190" s="11"/>
+      <c r="G190" s="12"/>
+      <c r="H190" s="10"/>
+      <c r="I190" s="12"/>
+      <c r="J190" s="10"/>
+      <c r="K190" s="11"/>
+      <c r="L190" s="11"/>
+      <c r="M190" s="11"/>
+      <c r="N190" s="12"/>
+      <c r="O190" s="10"/>
+      <c r="P190" s="11"/>
+      <c r="Q190" s="11"/>
+      <c r="R190" s="12"/>
+      <c r="S190" s="10"/>
+      <c r="T190" s="11"/>
+      <c r="U190" s="11"/>
+      <c r="V190" s="12"/>
+      <c r="W190" s="10"/>
+      <c r="X190" s="12"/>
+      <c r="Y190" s="10"/>
+      <c r="Z190" s="11"/>
+      <c r="AA190" s="11"/>
+      <c r="AB190" s="12"/>
     </row>
     <row r="191" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C191" s="5"/>
       <c r="D191" s="6"/>
       <c r="E191" s="2" t="s">
-        <v>181</v>
+        <v>10</v>
       </c>
       <c r="F191" s="5"/>
       <c r="G191" s="6"/>
       <c r="H191" s="2">
-        <v>1799</v>
+        <v>3499</v>
       </c>
       <c r="I191" s="6"/>
-      <c r="J191" s="16" t="s">
-        <v>23</v>
+      <c r="J191" s="13" t="s">
+        <v>11</v>
       </c>
       <c r="K191" s="5"/>
       <c r="L191" s="5"/>
       <c r="M191" s="5"/>
       <c r="N191" s="6"/>
       <c r="O191" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="P191" s="5"/>
       <c r="Q191" s="5"/>
       <c r="R191" s="6"/>
       <c r="S191" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T191" s="5"/>
       <c r="U191" s="5"/>
@@ -8445,8 +8427,8 @@
         <v>0</v>
       </c>
       <c r="X191" s="6"/>
-      <c r="Y191" s="17" t="s">
-        <v>189</v>
+      <c r="Y191" s="14" t="s">
+        <v>105</v>
       </c>
       <c r="Z191" s="5"/>
       <c r="AA191" s="5"/>
@@ -8514,24 +8496,24 @@
     </row>
     <row r="194" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C194" s="5"/>
       <c r="D194" s="6"/>
       <c r="E194" s="2" t="s">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="F194" s="5"/>
       <c r="G194" s="6"/>
       <c r="H194" s="2">
-        <v>3499</v>
+        <v>999</v>
       </c>
       <c r="I194" s="6"/>
-      <c r="J194" s="16" t="s">
-        <v>11</v>
+      <c r="J194" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="K194" s="5"/>
       <c r="L194" s="5"/>
@@ -8544,7 +8526,7 @@
       <c r="Q194" s="5"/>
       <c r="R194" s="6"/>
       <c r="S194" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T194" s="5"/>
       <c r="U194" s="5"/>
@@ -8553,8 +8535,8 @@
         <v>0</v>
       </c>
       <c r="X194" s="6"/>
-      <c r="Y194" s="17" t="s">
-        <v>106</v>
+      <c r="Y194" s="14" t="s">
+        <v>185</v>
       </c>
       <c r="Z194" s="5"/>
       <c r="AA194" s="5"/>
@@ -8620,562 +8602,123 @@
       <c r="AA196" s="11"/>
       <c r="AB196" s="12"/>
     </row>
-    <row r="197" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
-        <v>2</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C197" s="5"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F197" s="5"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="2">
-        <v>999</v>
-      </c>
-      <c r="I197" s="6"/>
-      <c r="J197" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K197" s="5"/>
-      <c r="L197" s="5"/>
-      <c r="M197" s="5"/>
-      <c r="N197" s="6"/>
-      <c r="O197" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="P197" s="5"/>
-      <c r="Q197" s="5"/>
-      <c r="R197" s="6"/>
-      <c r="S197" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T197" s="5"/>
-      <c r="U197" s="5"/>
-      <c r="V197" s="6"/>
-      <c r="W197" s="2">
-        <v>0</v>
-      </c>
-      <c r="X197" s="6"/>
-      <c r="Y197" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z197" s="5"/>
-      <c r="AA197" s="5"/>
-      <c r="AB197" s="6"/>
-    </row>
-    <row r="198" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A198" s="3"/>
-      <c r="B198" s="7"/>
-      <c r="C198" s="8"/>
-      <c r="D198" s="9"/>
-      <c r="E198" s="7"/>
-      <c r="F198" s="8"/>
-      <c r="G198" s="9"/>
-      <c r="H198" s="7"/>
-      <c r="I198" s="9"/>
-      <c r="J198" s="7"/>
-      <c r="K198" s="8"/>
-      <c r="L198" s="8"/>
-      <c r="M198" s="8"/>
-      <c r="N198" s="9"/>
-      <c r="O198" s="7"/>
-      <c r="P198" s="8"/>
-      <c r="Q198" s="8"/>
-      <c r="R198" s="9"/>
-      <c r="S198" s="7"/>
-      <c r="T198" s="8"/>
-      <c r="U198" s="8"/>
-      <c r="V198" s="9"/>
-      <c r="W198" s="7"/>
-      <c r="X198" s="9"/>
-      <c r="Y198" s="7"/>
-      <c r="Z198" s="8"/>
-      <c r="AA198" s="8"/>
-      <c r="AB198" s="9"/>
-    </row>
-    <row r="199" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A199" s="4"/>
-      <c r="B199" s="10"/>
-      <c r="C199" s="11"/>
-      <c r="D199" s="12"/>
-      <c r="E199" s="10"/>
-      <c r="F199" s="11"/>
-      <c r="G199" s="12"/>
-      <c r="H199" s="10"/>
-      <c r="I199" s="12"/>
-      <c r="J199" s="10"/>
-      <c r="K199" s="11"/>
-      <c r="L199" s="11"/>
-      <c r="M199" s="11"/>
-      <c r="N199" s="12"/>
-      <c r="O199" s="10"/>
-      <c r="P199" s="11"/>
-      <c r="Q199" s="11"/>
-      <c r="R199" s="12"/>
-      <c r="S199" s="10"/>
-      <c r="T199" s="11"/>
-      <c r="U199" s="11"/>
-      <c r="V199" s="12"/>
-      <c r="W199" s="10"/>
-      <c r="X199" s="12"/>
-      <c r="Y199" s="10"/>
-      <c r="Z199" s="11"/>
-      <c r="AA199" s="11"/>
-      <c r="AB199" s="12"/>
-    </row>
   </sheetData>
-  <mergeCells count="602">
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:D13"/>
-    <mergeCell ref="E11:G13"/>
-    <mergeCell ref="H11:I13"/>
-    <mergeCell ref="J11:N13"/>
-    <mergeCell ref="O11:R13"/>
-    <mergeCell ref="S11:V13"/>
-    <mergeCell ref="W11:X13"/>
-    <mergeCell ref="Y11:AB13"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:D7"/>
-    <mergeCell ref="E5:G7"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:N7"/>
-    <mergeCell ref="O5:R7"/>
-    <mergeCell ref="S5:V7"/>
-    <mergeCell ref="W5:X7"/>
-    <mergeCell ref="Y5:AB7"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:D4"/>
-    <mergeCell ref="E2:G4"/>
-    <mergeCell ref="H2:I4"/>
-    <mergeCell ref="J2:N4"/>
-    <mergeCell ref="O2:R4"/>
-    <mergeCell ref="S2:V4"/>
-    <mergeCell ref="W2:X4"/>
-    <mergeCell ref="Y2:AB4"/>
+  <mergeCells count="593">
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="H65:I67"/>
+    <mergeCell ref="J62:N64"/>
+    <mergeCell ref="S68:V70"/>
+    <mergeCell ref="E68:G70"/>
+    <mergeCell ref="H62:I64"/>
+    <mergeCell ref="J68:N70"/>
+    <mergeCell ref="B62:D64"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A17:A19"/>
     <mergeCell ref="A188:A190"/>
-    <mergeCell ref="B188:D190"/>
+    <mergeCell ref="J191:N193"/>
+    <mergeCell ref="H8:I10"/>
+    <mergeCell ref="B65:D67"/>
+    <mergeCell ref="W23:X25"/>
+    <mergeCell ref="H191:I193"/>
+    <mergeCell ref="E29:G31"/>
+    <mergeCell ref="H188:I190"/>
+    <mergeCell ref="B59:D61"/>
+    <mergeCell ref="O59:R61"/>
+    <mergeCell ref="W62:X64"/>
+    <mergeCell ref="E62:G64"/>
+    <mergeCell ref="J56:N58"/>
+    <mergeCell ref="E59:G61"/>
+    <mergeCell ref="O191:R193"/>
+    <mergeCell ref="O8:R10"/>
     <mergeCell ref="E188:G190"/>
-    <mergeCell ref="H188:I190"/>
-    <mergeCell ref="J188:N190"/>
+    <mergeCell ref="H50:I52"/>
+    <mergeCell ref="H23:I25"/>
+    <mergeCell ref="H32:I34"/>
+    <mergeCell ref="B17:D19"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="O44:R46"/>
+    <mergeCell ref="S35:V37"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="O194:R196"/>
+    <mergeCell ref="E194:G196"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="B194:D196"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="S194:V196"/>
     <mergeCell ref="O188:R190"/>
-    <mergeCell ref="S188:V190"/>
+    <mergeCell ref="H41:I43"/>
+    <mergeCell ref="E53:G55"/>
+    <mergeCell ref="O56:R58"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="B56:D58"/>
+    <mergeCell ref="O26:R28"/>
+    <mergeCell ref="O62:R64"/>
+    <mergeCell ref="B68:D70"/>
+    <mergeCell ref="E182:G184"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B8:D10"/>
+    <mergeCell ref="O182:R184"/>
+    <mergeCell ref="B182:D184"/>
+    <mergeCell ref="Y29:AB31"/>
+    <mergeCell ref="E191:G193"/>
+    <mergeCell ref="S29:V31"/>
+    <mergeCell ref="Y35:AB37"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="B44:D46"/>
+    <mergeCell ref="W191:X193"/>
+    <mergeCell ref="Y23:AB25"/>
     <mergeCell ref="W188:X190"/>
-    <mergeCell ref="Y188:AB190"/>
-    <mergeCell ref="Y14:AB16"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:D16"/>
-    <mergeCell ref="E14:G16"/>
-    <mergeCell ref="H14:I16"/>
-    <mergeCell ref="J14:N16"/>
-    <mergeCell ref="O14:R16"/>
-    <mergeCell ref="S14:V16"/>
-    <mergeCell ref="W14:X16"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="B182:D184"/>
-    <mergeCell ref="E182:G184"/>
-    <mergeCell ref="H182:I184"/>
-    <mergeCell ref="J182:N184"/>
-    <mergeCell ref="O182:R184"/>
-    <mergeCell ref="S182:V184"/>
-    <mergeCell ref="W182:X184"/>
+    <mergeCell ref="Y32:AB34"/>
+    <mergeCell ref="E8:G10"/>
+    <mergeCell ref="J1:N1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="S38:V40"/>
+    <mergeCell ref="W32:X34"/>
     <mergeCell ref="Y182:AB184"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="B179:D181"/>
-    <mergeCell ref="E179:G181"/>
-    <mergeCell ref="H179:I181"/>
-    <mergeCell ref="J179:N181"/>
-    <mergeCell ref="O179:R181"/>
-    <mergeCell ref="S179:V181"/>
-    <mergeCell ref="W179:X181"/>
-    <mergeCell ref="Y179:AB181"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="B176:D178"/>
-    <mergeCell ref="E176:G178"/>
-    <mergeCell ref="H176:I178"/>
-    <mergeCell ref="J176:N178"/>
-    <mergeCell ref="O176:R178"/>
-    <mergeCell ref="S176:V178"/>
-    <mergeCell ref="W176:X178"/>
-    <mergeCell ref="Y176:AB178"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="B173:D175"/>
-    <mergeCell ref="E173:G175"/>
-    <mergeCell ref="H173:I175"/>
-    <mergeCell ref="J173:N175"/>
-    <mergeCell ref="O173:R175"/>
-    <mergeCell ref="S173:V175"/>
-    <mergeCell ref="W173:X175"/>
-    <mergeCell ref="Y173:AB175"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="B170:D172"/>
-    <mergeCell ref="E170:G172"/>
-    <mergeCell ref="H170:I172"/>
-    <mergeCell ref="J170:N172"/>
-    <mergeCell ref="O170:R172"/>
-    <mergeCell ref="S170:V172"/>
-    <mergeCell ref="W170:X172"/>
-    <mergeCell ref="Y170:AB172"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="B167:D169"/>
-    <mergeCell ref="E167:G169"/>
-    <mergeCell ref="H167:I169"/>
-    <mergeCell ref="J167:N169"/>
-    <mergeCell ref="O167:R169"/>
-    <mergeCell ref="S167:V169"/>
-    <mergeCell ref="W167:X169"/>
-    <mergeCell ref="Y167:AB169"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="B164:D166"/>
-    <mergeCell ref="E164:G166"/>
-    <mergeCell ref="H164:I166"/>
-    <mergeCell ref="J164:N166"/>
-    <mergeCell ref="O164:R166"/>
-    <mergeCell ref="S164:V166"/>
-    <mergeCell ref="W164:X166"/>
-    <mergeCell ref="Y164:AB166"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="B161:D163"/>
-    <mergeCell ref="E161:G163"/>
-    <mergeCell ref="H161:I163"/>
-    <mergeCell ref="J161:N163"/>
-    <mergeCell ref="O161:R163"/>
-    <mergeCell ref="S161:V163"/>
-    <mergeCell ref="W161:X163"/>
-    <mergeCell ref="Y161:AB163"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="B158:D160"/>
-    <mergeCell ref="E158:G160"/>
-    <mergeCell ref="H158:I160"/>
-    <mergeCell ref="J158:N160"/>
-    <mergeCell ref="O158:R160"/>
-    <mergeCell ref="S158:V160"/>
-    <mergeCell ref="W158:X160"/>
-    <mergeCell ref="Y158:AB160"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="B155:D157"/>
-    <mergeCell ref="E155:G157"/>
-    <mergeCell ref="H155:I157"/>
-    <mergeCell ref="J155:N157"/>
-    <mergeCell ref="O155:R157"/>
-    <mergeCell ref="S155:V157"/>
-    <mergeCell ref="W155:X157"/>
-    <mergeCell ref="Y155:AB157"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="B152:D154"/>
-    <mergeCell ref="E152:G154"/>
-    <mergeCell ref="H152:I154"/>
-    <mergeCell ref="J152:N154"/>
-    <mergeCell ref="O152:R154"/>
-    <mergeCell ref="S152:V154"/>
-    <mergeCell ref="W152:X154"/>
-    <mergeCell ref="Y152:AB154"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="B149:D151"/>
-    <mergeCell ref="E149:G151"/>
-    <mergeCell ref="H149:I151"/>
-    <mergeCell ref="J149:N151"/>
-    <mergeCell ref="O149:R151"/>
-    <mergeCell ref="S149:V151"/>
-    <mergeCell ref="W149:X151"/>
-    <mergeCell ref="Y149:AB151"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="B146:D148"/>
-    <mergeCell ref="E146:G148"/>
-    <mergeCell ref="H146:I148"/>
-    <mergeCell ref="J146:N148"/>
-    <mergeCell ref="O146:R148"/>
-    <mergeCell ref="S146:V148"/>
-    <mergeCell ref="W146:X148"/>
-    <mergeCell ref="Y146:AB148"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="B143:D145"/>
-    <mergeCell ref="E143:G145"/>
-    <mergeCell ref="H143:I145"/>
-    <mergeCell ref="J143:N145"/>
-    <mergeCell ref="O143:R145"/>
-    <mergeCell ref="S143:V145"/>
-    <mergeCell ref="W143:X145"/>
-    <mergeCell ref="Y143:AB145"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="B140:D142"/>
-    <mergeCell ref="E140:G142"/>
-    <mergeCell ref="H140:I142"/>
-    <mergeCell ref="J140:N142"/>
-    <mergeCell ref="O140:R142"/>
-    <mergeCell ref="S140:V142"/>
-    <mergeCell ref="W140:X142"/>
-    <mergeCell ref="Y140:AB142"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="B137:D139"/>
-    <mergeCell ref="E137:G139"/>
-    <mergeCell ref="H137:I139"/>
-    <mergeCell ref="J137:N139"/>
-    <mergeCell ref="O137:R139"/>
-    <mergeCell ref="S137:V139"/>
-    <mergeCell ref="W137:X139"/>
-    <mergeCell ref="Y137:AB139"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="B134:D136"/>
-    <mergeCell ref="E134:G136"/>
-    <mergeCell ref="H134:I136"/>
-    <mergeCell ref="J134:N136"/>
-    <mergeCell ref="O134:R136"/>
-    <mergeCell ref="S134:V136"/>
-    <mergeCell ref="W134:X136"/>
-    <mergeCell ref="Y134:AB136"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="B131:D133"/>
-    <mergeCell ref="E131:G133"/>
-    <mergeCell ref="H131:I133"/>
-    <mergeCell ref="J131:N133"/>
-    <mergeCell ref="O131:R133"/>
-    <mergeCell ref="S131:V133"/>
-    <mergeCell ref="W131:X133"/>
-    <mergeCell ref="Y131:AB133"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="B128:D130"/>
-    <mergeCell ref="E128:G130"/>
-    <mergeCell ref="H128:I130"/>
-    <mergeCell ref="J128:N130"/>
-    <mergeCell ref="O128:R130"/>
-    <mergeCell ref="S128:V130"/>
-    <mergeCell ref="W128:X130"/>
-    <mergeCell ref="Y128:AB130"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="B125:D127"/>
-    <mergeCell ref="E125:G127"/>
-    <mergeCell ref="H125:I127"/>
-    <mergeCell ref="J125:N127"/>
-    <mergeCell ref="O125:R127"/>
-    <mergeCell ref="S125:V127"/>
-    <mergeCell ref="W125:X127"/>
-    <mergeCell ref="Y125:AB127"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="B122:D124"/>
-    <mergeCell ref="E122:G124"/>
-    <mergeCell ref="H122:I124"/>
-    <mergeCell ref="J122:N124"/>
-    <mergeCell ref="O122:R124"/>
-    <mergeCell ref="S122:V124"/>
-    <mergeCell ref="W122:X124"/>
-    <mergeCell ref="Y122:AB124"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="B119:D121"/>
-    <mergeCell ref="E119:G121"/>
-    <mergeCell ref="H119:I121"/>
-    <mergeCell ref="J119:N121"/>
-    <mergeCell ref="O119:R121"/>
-    <mergeCell ref="S119:V121"/>
-    <mergeCell ref="W119:X121"/>
-    <mergeCell ref="Y119:AB121"/>
-    <mergeCell ref="A116:A118"/>
-    <mergeCell ref="B116:D118"/>
-    <mergeCell ref="E116:G118"/>
-    <mergeCell ref="H116:I118"/>
-    <mergeCell ref="J116:N118"/>
-    <mergeCell ref="O116:R118"/>
-    <mergeCell ref="S116:V118"/>
-    <mergeCell ref="W116:X118"/>
-    <mergeCell ref="Y116:AB118"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="B113:D115"/>
-    <mergeCell ref="E113:G115"/>
-    <mergeCell ref="H113:I115"/>
-    <mergeCell ref="J113:N115"/>
-    <mergeCell ref="O113:R115"/>
-    <mergeCell ref="S113:V115"/>
-    <mergeCell ref="W113:X115"/>
-    <mergeCell ref="Y113:AB115"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="B110:D112"/>
-    <mergeCell ref="E110:G112"/>
-    <mergeCell ref="H110:I112"/>
-    <mergeCell ref="J110:N112"/>
-    <mergeCell ref="O110:R112"/>
-    <mergeCell ref="S110:V112"/>
-    <mergeCell ref="W110:X112"/>
-    <mergeCell ref="Y110:AB112"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="B107:D109"/>
-    <mergeCell ref="E107:G109"/>
-    <mergeCell ref="H107:I109"/>
-    <mergeCell ref="J107:N109"/>
-    <mergeCell ref="O107:R109"/>
-    <mergeCell ref="S107:V109"/>
-    <mergeCell ref="W107:X109"/>
-    <mergeCell ref="Y107:AB109"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="B104:D106"/>
-    <mergeCell ref="E104:G106"/>
-    <mergeCell ref="H104:I106"/>
-    <mergeCell ref="J104:N106"/>
-    <mergeCell ref="O104:R106"/>
-    <mergeCell ref="S104:V106"/>
-    <mergeCell ref="W104:X106"/>
-    <mergeCell ref="Y104:AB106"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="B101:D103"/>
-    <mergeCell ref="E101:G103"/>
-    <mergeCell ref="H101:I103"/>
-    <mergeCell ref="J101:N103"/>
-    <mergeCell ref="O101:R103"/>
-    <mergeCell ref="S101:V103"/>
-    <mergeCell ref="W101:X103"/>
-    <mergeCell ref="Y101:AB103"/>
-    <mergeCell ref="A98:A100"/>
-    <mergeCell ref="B98:D100"/>
-    <mergeCell ref="E98:G100"/>
-    <mergeCell ref="H98:I100"/>
-    <mergeCell ref="J98:N100"/>
-    <mergeCell ref="O98:R100"/>
-    <mergeCell ref="S98:V100"/>
-    <mergeCell ref="W98:X100"/>
-    <mergeCell ref="Y98:AB100"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="B95:D97"/>
-    <mergeCell ref="E95:G97"/>
-    <mergeCell ref="H95:I97"/>
-    <mergeCell ref="J95:N97"/>
-    <mergeCell ref="O95:R97"/>
-    <mergeCell ref="S95:V97"/>
-    <mergeCell ref="W95:X97"/>
-    <mergeCell ref="Y95:AB97"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="B92:D94"/>
-    <mergeCell ref="E92:G94"/>
-    <mergeCell ref="H92:I94"/>
-    <mergeCell ref="J92:N94"/>
-    <mergeCell ref="O92:R94"/>
-    <mergeCell ref="S92:V94"/>
-    <mergeCell ref="W92:X94"/>
-    <mergeCell ref="Y92:AB94"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="B89:D91"/>
-    <mergeCell ref="E89:G91"/>
-    <mergeCell ref="H89:I91"/>
-    <mergeCell ref="J89:N91"/>
-    <mergeCell ref="O89:R91"/>
-    <mergeCell ref="S89:V91"/>
-    <mergeCell ref="W89:X91"/>
-    <mergeCell ref="Y89:AB91"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="B86:D88"/>
-    <mergeCell ref="E86:G88"/>
-    <mergeCell ref="H86:I88"/>
-    <mergeCell ref="J86:N88"/>
-    <mergeCell ref="O86:R88"/>
-    <mergeCell ref="S86:V88"/>
-    <mergeCell ref="W86:X88"/>
-    <mergeCell ref="Y86:AB88"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="B83:D85"/>
-    <mergeCell ref="E83:G85"/>
-    <mergeCell ref="H83:I85"/>
-    <mergeCell ref="J83:N85"/>
-    <mergeCell ref="O83:R85"/>
-    <mergeCell ref="S83:V85"/>
-    <mergeCell ref="W83:X85"/>
-    <mergeCell ref="Y83:AB85"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="B80:D82"/>
-    <mergeCell ref="E80:G82"/>
-    <mergeCell ref="H80:I82"/>
-    <mergeCell ref="J80:N82"/>
-    <mergeCell ref="O80:R82"/>
-    <mergeCell ref="S80:V82"/>
-    <mergeCell ref="W80:X82"/>
-    <mergeCell ref="Y80:AB82"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:D79"/>
-    <mergeCell ref="E77:G79"/>
-    <mergeCell ref="H77:I79"/>
-    <mergeCell ref="J77:N79"/>
-    <mergeCell ref="O77:R79"/>
-    <mergeCell ref="S77:V79"/>
-    <mergeCell ref="W77:X79"/>
-    <mergeCell ref="Y77:AB79"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="B74:D76"/>
-    <mergeCell ref="E74:G76"/>
-    <mergeCell ref="H74:I76"/>
-    <mergeCell ref="J74:N76"/>
-    <mergeCell ref="O74:R76"/>
-    <mergeCell ref="S74:V76"/>
-    <mergeCell ref="W74:X76"/>
-    <mergeCell ref="Y74:AB76"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="B71:D73"/>
-    <mergeCell ref="E71:G73"/>
-    <mergeCell ref="H71:I73"/>
-    <mergeCell ref="J71:N73"/>
-    <mergeCell ref="O71:R73"/>
-    <mergeCell ref="S71:V73"/>
-    <mergeCell ref="W71:X73"/>
-    <mergeCell ref="Y71:AB73"/>
-    <mergeCell ref="J65:N67"/>
-    <mergeCell ref="S47:V49"/>
-    <mergeCell ref="W56:X58"/>
-    <mergeCell ref="Y68:AB70"/>
-    <mergeCell ref="E38:G40"/>
-    <mergeCell ref="W20:X22"/>
-    <mergeCell ref="E47:G49"/>
-    <mergeCell ref="S53:V55"/>
-    <mergeCell ref="J191:N193"/>
-    <mergeCell ref="W59:X61"/>
-    <mergeCell ref="O23:R25"/>
-    <mergeCell ref="J44:N46"/>
-    <mergeCell ref="S17:V19"/>
-    <mergeCell ref="J59:N61"/>
-    <mergeCell ref="O32:R34"/>
-    <mergeCell ref="Y41:AB43"/>
-    <mergeCell ref="H59:I61"/>
-    <mergeCell ref="E65:G67"/>
-    <mergeCell ref="Y20:AB22"/>
-    <mergeCell ref="H68:I70"/>
-    <mergeCell ref="W185:X187"/>
-    <mergeCell ref="Y65:AB67"/>
-    <mergeCell ref="O65:R67"/>
-    <mergeCell ref="J53:N55"/>
-    <mergeCell ref="Y8:AB10"/>
-    <mergeCell ref="S41:V43"/>
-    <mergeCell ref="H38:I40"/>
-    <mergeCell ref="S20:V22"/>
-    <mergeCell ref="Y44:AB46"/>
-    <mergeCell ref="S185:V187"/>
-    <mergeCell ref="O41:R43"/>
-    <mergeCell ref="J197:N199"/>
-    <mergeCell ref="S44:V46"/>
-    <mergeCell ref="S8:V10"/>
-    <mergeCell ref="W8:X10"/>
-    <mergeCell ref="S62:V64"/>
-    <mergeCell ref="W17:X19"/>
+    <mergeCell ref="Y191:AB193"/>
+    <mergeCell ref="Y17:AB19"/>
+    <mergeCell ref="Y26:AB28"/>
     <mergeCell ref="B191:D193"/>
-    <mergeCell ref="S59:V61"/>
-    <mergeCell ref="S56:V58"/>
-    <mergeCell ref="W29:X31"/>
-    <mergeCell ref="W38:X40"/>
-    <mergeCell ref="Y56:AB58"/>
-    <mergeCell ref="W41:X43"/>
-    <mergeCell ref="W50:X52"/>
-    <mergeCell ref="H35:I37"/>
-    <mergeCell ref="E41:G43"/>
-    <mergeCell ref="E56:G58"/>
-    <mergeCell ref="J185:N187"/>
-    <mergeCell ref="J26:N28"/>
-    <mergeCell ref="O17:R19"/>
-    <mergeCell ref="J35:N37"/>
-    <mergeCell ref="Y62:AB64"/>
-    <mergeCell ref="Y59:AB61"/>
-    <mergeCell ref="W53:X55"/>
-    <mergeCell ref="W44:X46"/>
-    <mergeCell ref="H29:I31"/>
-    <mergeCell ref="E20:G22"/>
-    <mergeCell ref="H47:I49"/>
+    <mergeCell ref="H20:I22"/>
+    <mergeCell ref="B53:D55"/>
+    <mergeCell ref="E50:G52"/>
+    <mergeCell ref="S191:V193"/>
+    <mergeCell ref="B23:D25"/>
+    <mergeCell ref="E26:G28"/>
+    <mergeCell ref="E35:G37"/>
+    <mergeCell ref="H44:I46"/>
+    <mergeCell ref="O38:R40"/>
+    <mergeCell ref="O47:R49"/>
+    <mergeCell ref="J23:N25"/>
+    <mergeCell ref="J20:N22"/>
+    <mergeCell ref="S65:V67"/>
+    <mergeCell ref="B47:D49"/>
+    <mergeCell ref="S50:V52"/>
+    <mergeCell ref="O20:R22"/>
+    <mergeCell ref="S26:V28"/>
+    <mergeCell ref="B50:D52"/>
+    <mergeCell ref="Y38:AB40"/>
+    <mergeCell ref="S23:V25"/>
+    <mergeCell ref="S32:V34"/>
+    <mergeCell ref="O29:R31"/>
+    <mergeCell ref="Y50:AB52"/>
+    <mergeCell ref="W47:X49"/>
+    <mergeCell ref="B20:D22"/>
+    <mergeCell ref="J47:N49"/>
+    <mergeCell ref="E32:G34"/>
+    <mergeCell ref="Y47:AB49"/>
+    <mergeCell ref="W26:X28"/>
+    <mergeCell ref="W35:X37"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="O68:R70"/>
     <mergeCell ref="B26:D28"/>
@@ -9200,138 +8743,460 @@
     <mergeCell ref="J32:N34"/>
     <mergeCell ref="O50:R52"/>
     <mergeCell ref="H26:I28"/>
+    <mergeCell ref="B188:D190"/>
+    <mergeCell ref="S59:V61"/>
+    <mergeCell ref="S56:V58"/>
+    <mergeCell ref="W29:X31"/>
+    <mergeCell ref="W38:X40"/>
+    <mergeCell ref="Y56:AB58"/>
+    <mergeCell ref="W41:X43"/>
+    <mergeCell ref="W50:X52"/>
+    <mergeCell ref="H35:I37"/>
+    <mergeCell ref="E41:G43"/>
+    <mergeCell ref="E56:G58"/>
+    <mergeCell ref="J182:N184"/>
+    <mergeCell ref="J35:N37"/>
+    <mergeCell ref="Y62:AB64"/>
+    <mergeCell ref="Y59:AB61"/>
+    <mergeCell ref="W53:X55"/>
+    <mergeCell ref="W44:X46"/>
+    <mergeCell ref="H29:I31"/>
+    <mergeCell ref="H47:I49"/>
     <mergeCell ref="H56:I58"/>
-    <mergeCell ref="J17:N19"/>
     <mergeCell ref="B41:D43"/>
     <mergeCell ref="Y53:AB55"/>
+    <mergeCell ref="E44:G46"/>
+    <mergeCell ref="S188:V190"/>
+    <mergeCell ref="Y8:AB10"/>
+    <mergeCell ref="S41:V43"/>
+    <mergeCell ref="H38:I40"/>
+    <mergeCell ref="S20:V22"/>
+    <mergeCell ref="Y44:AB46"/>
+    <mergeCell ref="S182:V184"/>
+    <mergeCell ref="O41:R43"/>
+    <mergeCell ref="J194:N196"/>
+    <mergeCell ref="S44:V46"/>
+    <mergeCell ref="S8:V10"/>
+    <mergeCell ref="W8:X10"/>
+    <mergeCell ref="S62:V64"/>
+    <mergeCell ref="W17:X19"/>
+    <mergeCell ref="J26:N28"/>
+    <mergeCell ref="O17:R19"/>
+    <mergeCell ref="J17:N19"/>
+    <mergeCell ref="H182:I184"/>
+    <mergeCell ref="J8:N10"/>
+    <mergeCell ref="H194:I196"/>
+    <mergeCell ref="H17:I19"/>
+    <mergeCell ref="Y194:AB196"/>
+    <mergeCell ref="Y188:AB190"/>
+    <mergeCell ref="W194:X196"/>
+    <mergeCell ref="W65:X67"/>
+    <mergeCell ref="S17:V19"/>
+    <mergeCell ref="J59:N61"/>
+    <mergeCell ref="O32:R34"/>
+    <mergeCell ref="Y41:AB43"/>
+    <mergeCell ref="H59:I61"/>
+    <mergeCell ref="E65:G67"/>
+    <mergeCell ref="Y20:AB22"/>
+    <mergeCell ref="H68:I70"/>
+    <mergeCell ref="W182:X184"/>
+    <mergeCell ref="Y65:AB67"/>
+    <mergeCell ref="O65:R67"/>
+    <mergeCell ref="J53:N55"/>
+    <mergeCell ref="E20:G22"/>
     <mergeCell ref="E23:G25"/>
-    <mergeCell ref="E44:G46"/>
-    <mergeCell ref="S191:V193"/>
-    <mergeCell ref="B47:D49"/>
-    <mergeCell ref="S50:V52"/>
-    <mergeCell ref="O20:R22"/>
-    <mergeCell ref="S26:V28"/>
-    <mergeCell ref="B50:D52"/>
-    <mergeCell ref="Y38:AB40"/>
-    <mergeCell ref="S23:V25"/>
-    <mergeCell ref="S32:V34"/>
-    <mergeCell ref="O29:R31"/>
-    <mergeCell ref="Y50:AB52"/>
-    <mergeCell ref="W47:X49"/>
-    <mergeCell ref="B20:D22"/>
-    <mergeCell ref="J47:N49"/>
+    <mergeCell ref="E17:G19"/>
+    <mergeCell ref="W68:X70"/>
+    <mergeCell ref="J65:N67"/>
+    <mergeCell ref="S47:V49"/>
+    <mergeCell ref="W56:X58"/>
+    <mergeCell ref="Y68:AB70"/>
+    <mergeCell ref="E38:G40"/>
+    <mergeCell ref="W20:X22"/>
+    <mergeCell ref="E47:G49"/>
+    <mergeCell ref="S53:V55"/>
+    <mergeCell ref="J188:N190"/>
+    <mergeCell ref="W59:X61"/>
+    <mergeCell ref="O23:R25"/>
+    <mergeCell ref="J44:N46"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="B71:D73"/>
+    <mergeCell ref="E71:G73"/>
+    <mergeCell ref="H71:I73"/>
+    <mergeCell ref="J71:N73"/>
+    <mergeCell ref="O71:R73"/>
+    <mergeCell ref="S71:V73"/>
+    <mergeCell ref="W71:X73"/>
+    <mergeCell ref="Y71:AB73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="B74:D76"/>
+    <mergeCell ref="E74:G76"/>
+    <mergeCell ref="H74:I76"/>
+    <mergeCell ref="J74:N76"/>
+    <mergeCell ref="O74:R76"/>
+    <mergeCell ref="S74:V76"/>
+    <mergeCell ref="W74:X76"/>
+    <mergeCell ref="Y74:AB76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:D79"/>
+    <mergeCell ref="E77:G79"/>
+    <mergeCell ref="H77:I79"/>
+    <mergeCell ref="J77:N79"/>
+    <mergeCell ref="O77:R79"/>
+    <mergeCell ref="S77:V79"/>
+    <mergeCell ref="W77:X79"/>
+    <mergeCell ref="Y77:AB79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="B80:D82"/>
+    <mergeCell ref="E80:G82"/>
+    <mergeCell ref="H80:I82"/>
+    <mergeCell ref="J80:N82"/>
+    <mergeCell ref="O80:R82"/>
+    <mergeCell ref="S80:V82"/>
+    <mergeCell ref="W80:X82"/>
+    <mergeCell ref="Y80:AB82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="B83:D85"/>
+    <mergeCell ref="E83:G85"/>
+    <mergeCell ref="H83:I85"/>
+    <mergeCell ref="J83:N85"/>
+    <mergeCell ref="O83:R85"/>
+    <mergeCell ref="S83:V85"/>
+    <mergeCell ref="W83:X85"/>
+    <mergeCell ref="Y83:AB85"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="B86:D88"/>
+    <mergeCell ref="E86:G88"/>
+    <mergeCell ref="H86:I88"/>
+    <mergeCell ref="J86:N88"/>
+    <mergeCell ref="O86:R88"/>
+    <mergeCell ref="S86:V88"/>
+    <mergeCell ref="W86:X88"/>
+    <mergeCell ref="Y86:AB88"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="B89:D91"/>
+    <mergeCell ref="E89:G91"/>
+    <mergeCell ref="H89:I91"/>
+    <mergeCell ref="J89:N91"/>
+    <mergeCell ref="O89:R91"/>
+    <mergeCell ref="S89:V91"/>
+    <mergeCell ref="W89:X91"/>
+    <mergeCell ref="Y89:AB91"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="B92:D94"/>
+    <mergeCell ref="E92:G94"/>
+    <mergeCell ref="H92:I94"/>
+    <mergeCell ref="J92:N94"/>
+    <mergeCell ref="O92:R94"/>
+    <mergeCell ref="S92:V94"/>
+    <mergeCell ref="W92:X94"/>
+    <mergeCell ref="Y92:AB94"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="B95:D97"/>
+    <mergeCell ref="E95:G97"/>
+    <mergeCell ref="H95:I97"/>
+    <mergeCell ref="J95:N97"/>
+    <mergeCell ref="O95:R97"/>
+    <mergeCell ref="S95:V97"/>
+    <mergeCell ref="W95:X97"/>
+    <mergeCell ref="Y95:AB97"/>
+    <mergeCell ref="A98:A100"/>
+    <mergeCell ref="B98:D100"/>
+    <mergeCell ref="E98:G100"/>
+    <mergeCell ref="H98:I100"/>
+    <mergeCell ref="J98:N100"/>
+    <mergeCell ref="O98:R100"/>
+    <mergeCell ref="S98:V100"/>
+    <mergeCell ref="W98:X100"/>
+    <mergeCell ref="Y98:AB100"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="B101:D103"/>
+    <mergeCell ref="E101:G103"/>
+    <mergeCell ref="H101:I103"/>
+    <mergeCell ref="J101:N103"/>
+    <mergeCell ref="O101:R103"/>
+    <mergeCell ref="S101:V103"/>
+    <mergeCell ref="W101:X103"/>
+    <mergeCell ref="Y101:AB103"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="B104:D106"/>
+    <mergeCell ref="E104:G106"/>
+    <mergeCell ref="H104:I106"/>
+    <mergeCell ref="J104:N106"/>
+    <mergeCell ref="O104:R106"/>
+    <mergeCell ref="S104:V106"/>
+    <mergeCell ref="W104:X106"/>
+    <mergeCell ref="Y104:AB106"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="B107:D109"/>
+    <mergeCell ref="E107:G109"/>
+    <mergeCell ref="H107:I109"/>
+    <mergeCell ref="J107:N109"/>
+    <mergeCell ref="O107:R109"/>
+    <mergeCell ref="S107:V109"/>
+    <mergeCell ref="W107:X109"/>
+    <mergeCell ref="Y107:AB109"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="B110:D112"/>
+    <mergeCell ref="E110:G112"/>
+    <mergeCell ref="H110:I112"/>
+    <mergeCell ref="J110:N112"/>
+    <mergeCell ref="O110:R112"/>
+    <mergeCell ref="S110:V112"/>
+    <mergeCell ref="W110:X112"/>
+    <mergeCell ref="Y110:AB112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="B113:D115"/>
+    <mergeCell ref="E113:G115"/>
+    <mergeCell ref="H113:I115"/>
+    <mergeCell ref="J113:N115"/>
+    <mergeCell ref="O113:R115"/>
+    <mergeCell ref="S113:V115"/>
+    <mergeCell ref="W113:X115"/>
+    <mergeCell ref="Y113:AB115"/>
+    <mergeCell ref="A116:A118"/>
+    <mergeCell ref="B116:D118"/>
+    <mergeCell ref="E116:G118"/>
+    <mergeCell ref="H116:I118"/>
+    <mergeCell ref="J116:N118"/>
+    <mergeCell ref="O116:R118"/>
+    <mergeCell ref="S116:V118"/>
+    <mergeCell ref="W116:X118"/>
+    <mergeCell ref="Y116:AB118"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="B119:D121"/>
+    <mergeCell ref="E119:G121"/>
+    <mergeCell ref="H119:I121"/>
+    <mergeCell ref="J119:N121"/>
+    <mergeCell ref="O119:R121"/>
+    <mergeCell ref="S119:V121"/>
+    <mergeCell ref="W119:X121"/>
+    <mergeCell ref="Y119:AB121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="B122:D124"/>
+    <mergeCell ref="E122:G124"/>
+    <mergeCell ref="H122:I124"/>
+    <mergeCell ref="J122:N124"/>
+    <mergeCell ref="O122:R124"/>
+    <mergeCell ref="S122:V124"/>
+    <mergeCell ref="W122:X124"/>
+    <mergeCell ref="Y122:AB124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="B125:D127"/>
+    <mergeCell ref="E125:G127"/>
+    <mergeCell ref="H125:I127"/>
+    <mergeCell ref="J125:N127"/>
+    <mergeCell ref="O125:R127"/>
+    <mergeCell ref="S125:V127"/>
+    <mergeCell ref="W125:X127"/>
+    <mergeCell ref="Y125:AB127"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="B128:D130"/>
+    <mergeCell ref="E128:G130"/>
+    <mergeCell ref="H128:I130"/>
+    <mergeCell ref="J128:N130"/>
+    <mergeCell ref="O128:R130"/>
+    <mergeCell ref="S128:V130"/>
+    <mergeCell ref="W128:X130"/>
+    <mergeCell ref="Y128:AB130"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="B131:D133"/>
+    <mergeCell ref="E131:G133"/>
+    <mergeCell ref="H131:I133"/>
+    <mergeCell ref="J131:N133"/>
+    <mergeCell ref="O131:R133"/>
+    <mergeCell ref="S131:V133"/>
+    <mergeCell ref="W131:X133"/>
+    <mergeCell ref="Y131:AB133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="B134:D136"/>
+    <mergeCell ref="E134:G136"/>
+    <mergeCell ref="H134:I136"/>
+    <mergeCell ref="J134:N136"/>
+    <mergeCell ref="O134:R136"/>
+    <mergeCell ref="S134:V136"/>
+    <mergeCell ref="W134:X136"/>
+    <mergeCell ref="Y134:AB136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="B137:D139"/>
+    <mergeCell ref="E137:G139"/>
+    <mergeCell ref="H137:I139"/>
+    <mergeCell ref="J137:N139"/>
+    <mergeCell ref="O137:R139"/>
+    <mergeCell ref="S137:V139"/>
+    <mergeCell ref="W137:X139"/>
+    <mergeCell ref="Y137:AB139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="B140:D142"/>
+    <mergeCell ref="E140:G142"/>
+    <mergeCell ref="H140:I142"/>
+    <mergeCell ref="J140:N142"/>
+    <mergeCell ref="O140:R142"/>
+    <mergeCell ref="S140:V142"/>
+    <mergeCell ref="W140:X142"/>
+    <mergeCell ref="Y140:AB142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="B143:D145"/>
+    <mergeCell ref="E143:G145"/>
+    <mergeCell ref="H143:I145"/>
+    <mergeCell ref="J143:N145"/>
+    <mergeCell ref="O143:R145"/>
+    <mergeCell ref="S143:V145"/>
+    <mergeCell ref="W143:X145"/>
+    <mergeCell ref="Y143:AB145"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="B146:D148"/>
+    <mergeCell ref="E146:G148"/>
+    <mergeCell ref="H146:I148"/>
+    <mergeCell ref="J146:N148"/>
+    <mergeCell ref="O146:R148"/>
+    <mergeCell ref="S146:V148"/>
+    <mergeCell ref="W146:X148"/>
+    <mergeCell ref="Y146:AB148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="B149:D151"/>
+    <mergeCell ref="E149:G151"/>
+    <mergeCell ref="H149:I151"/>
+    <mergeCell ref="J149:N151"/>
+    <mergeCell ref="O149:R151"/>
+    <mergeCell ref="S149:V151"/>
+    <mergeCell ref="W149:X151"/>
+    <mergeCell ref="Y149:AB151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="B152:D154"/>
+    <mergeCell ref="E152:G154"/>
+    <mergeCell ref="H152:I154"/>
+    <mergeCell ref="J152:N154"/>
+    <mergeCell ref="O152:R154"/>
+    <mergeCell ref="S152:V154"/>
+    <mergeCell ref="W152:X154"/>
+    <mergeCell ref="Y152:AB154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="B155:D157"/>
+    <mergeCell ref="E155:G157"/>
+    <mergeCell ref="H155:I157"/>
+    <mergeCell ref="J155:N157"/>
+    <mergeCell ref="O155:R157"/>
+    <mergeCell ref="S155:V157"/>
+    <mergeCell ref="W155:X157"/>
+    <mergeCell ref="Y155:AB157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="B158:D160"/>
+    <mergeCell ref="E158:G160"/>
+    <mergeCell ref="H158:I160"/>
+    <mergeCell ref="J158:N160"/>
+    <mergeCell ref="O158:R160"/>
+    <mergeCell ref="S158:V160"/>
+    <mergeCell ref="W158:X160"/>
+    <mergeCell ref="Y158:AB160"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="B161:D163"/>
+    <mergeCell ref="E161:G163"/>
+    <mergeCell ref="H161:I163"/>
+    <mergeCell ref="J161:N163"/>
+    <mergeCell ref="O161:R163"/>
+    <mergeCell ref="S161:V163"/>
+    <mergeCell ref="W161:X163"/>
+    <mergeCell ref="Y161:AB163"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="B164:D166"/>
+    <mergeCell ref="E164:G166"/>
+    <mergeCell ref="H164:I166"/>
+    <mergeCell ref="J164:N166"/>
+    <mergeCell ref="O164:R166"/>
+    <mergeCell ref="S164:V166"/>
+    <mergeCell ref="W164:X166"/>
+    <mergeCell ref="Y164:AB166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="B167:D169"/>
+    <mergeCell ref="E167:G169"/>
+    <mergeCell ref="H167:I169"/>
+    <mergeCell ref="J167:N169"/>
+    <mergeCell ref="O167:R169"/>
+    <mergeCell ref="S167:V169"/>
+    <mergeCell ref="W167:X169"/>
+    <mergeCell ref="Y167:AB169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="B170:D172"/>
+    <mergeCell ref="E170:G172"/>
+    <mergeCell ref="H170:I172"/>
+    <mergeCell ref="J170:N172"/>
+    <mergeCell ref="O170:R172"/>
+    <mergeCell ref="S170:V172"/>
+    <mergeCell ref="W170:X172"/>
+    <mergeCell ref="Y170:AB172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="B173:D175"/>
+    <mergeCell ref="E173:G175"/>
+    <mergeCell ref="H173:I175"/>
+    <mergeCell ref="J173:N175"/>
+    <mergeCell ref="O173:R175"/>
+    <mergeCell ref="S173:V175"/>
+    <mergeCell ref="W173:X175"/>
+    <mergeCell ref="Y173:AB175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="B176:D178"/>
+    <mergeCell ref="E176:G178"/>
+    <mergeCell ref="H176:I178"/>
+    <mergeCell ref="J176:N178"/>
+    <mergeCell ref="O176:R178"/>
+    <mergeCell ref="S176:V178"/>
+    <mergeCell ref="W176:X178"/>
+    <mergeCell ref="Y176:AB178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="B179:D181"/>
+    <mergeCell ref="E179:G181"/>
+    <mergeCell ref="H179:I181"/>
+    <mergeCell ref="J179:N181"/>
+    <mergeCell ref="O179:R181"/>
+    <mergeCell ref="S179:V181"/>
+    <mergeCell ref="W179:X181"/>
+    <mergeCell ref="Y179:AB181"/>
+    <mergeCell ref="Y14:AB16"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:D16"/>
+    <mergeCell ref="E14:G16"/>
+    <mergeCell ref="H14:I16"/>
+    <mergeCell ref="J14:N16"/>
+    <mergeCell ref="O14:R16"/>
+    <mergeCell ref="S14:V16"/>
+    <mergeCell ref="W14:X16"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="B185:D187"/>
+    <mergeCell ref="E185:G187"/>
     <mergeCell ref="H185:I187"/>
-    <mergeCell ref="E32:G34"/>
-    <mergeCell ref="Y47:AB49"/>
-    <mergeCell ref="B194:D196"/>
-    <mergeCell ref="H20:I22"/>
-    <mergeCell ref="B53:D55"/>
-    <mergeCell ref="E50:G52"/>
-    <mergeCell ref="S194:V196"/>
-    <mergeCell ref="B23:D25"/>
-    <mergeCell ref="E26:G28"/>
-    <mergeCell ref="E35:G37"/>
-    <mergeCell ref="H44:I46"/>
-    <mergeCell ref="E17:G19"/>
-    <mergeCell ref="O38:R40"/>
-    <mergeCell ref="O47:R49"/>
-    <mergeCell ref="J8:N10"/>
-    <mergeCell ref="H197:I199"/>
-    <mergeCell ref="H17:I19"/>
-    <mergeCell ref="J23:N25"/>
-    <mergeCell ref="B8:D10"/>
+    <mergeCell ref="J185:N187"/>
     <mergeCell ref="O185:R187"/>
-    <mergeCell ref="B185:D187"/>
-    <mergeCell ref="Y29:AB31"/>
-    <mergeCell ref="E194:G196"/>
-    <mergeCell ref="S29:V31"/>
-    <mergeCell ref="Y35:AB37"/>
-    <mergeCell ref="Y1:AB1"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="B44:D46"/>
-    <mergeCell ref="W194:X196"/>
-    <mergeCell ref="Y23:AB25"/>
-    <mergeCell ref="W191:X193"/>
-    <mergeCell ref="Y32:AB34"/>
-    <mergeCell ref="E8:G10"/>
-    <mergeCell ref="J1:N1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="S38:V40"/>
-    <mergeCell ref="W32:X34"/>
-    <mergeCell ref="Y197:AB199"/>
+    <mergeCell ref="S185:V187"/>
+    <mergeCell ref="W185:X187"/>
     <mergeCell ref="Y185:AB187"/>
-    <mergeCell ref="Y194:AB196"/>
-    <mergeCell ref="Y17:AB19"/>
-    <mergeCell ref="Y26:AB28"/>
-    <mergeCell ref="Y191:AB193"/>
-    <mergeCell ref="J20:N22"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="O44:R46"/>
-    <mergeCell ref="S35:V37"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="O197:R199"/>
-    <mergeCell ref="E197:G199"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="B197:D199"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="J194:N196"/>
-    <mergeCell ref="H8:I10"/>
-    <mergeCell ref="B65:D67"/>
-    <mergeCell ref="W23:X25"/>
-    <mergeCell ref="H194:I196"/>
-    <mergeCell ref="E29:G31"/>
-    <mergeCell ref="H191:I193"/>
-    <mergeCell ref="B59:D61"/>
-    <mergeCell ref="O59:R61"/>
-    <mergeCell ref="W62:X64"/>
-    <mergeCell ref="E62:G64"/>
-    <mergeCell ref="J56:N58"/>
-    <mergeCell ref="E59:G61"/>
-    <mergeCell ref="O194:R196"/>
-    <mergeCell ref="O8:R10"/>
-    <mergeCell ref="W197:X199"/>
-    <mergeCell ref="E191:G193"/>
-    <mergeCell ref="H50:I52"/>
-    <mergeCell ref="H23:I25"/>
-    <mergeCell ref="H32:I34"/>
-    <mergeCell ref="S197:V199"/>
-    <mergeCell ref="B17:D19"/>
-    <mergeCell ref="O191:R193"/>
-    <mergeCell ref="H41:I43"/>
-    <mergeCell ref="E53:G55"/>
-    <mergeCell ref="O56:R58"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B56:D58"/>
-    <mergeCell ref="O26:R28"/>
-    <mergeCell ref="O62:R64"/>
-    <mergeCell ref="B68:D70"/>
-    <mergeCell ref="E185:G187"/>
-    <mergeCell ref="W26:X28"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="W35:X37"/>
-    <mergeCell ref="S65:V67"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="H65:I67"/>
-    <mergeCell ref="J62:N64"/>
-    <mergeCell ref="S68:V70"/>
-    <mergeCell ref="E68:G70"/>
-    <mergeCell ref="H62:I64"/>
-    <mergeCell ref="J68:N70"/>
-    <mergeCell ref="W65:X67"/>
-    <mergeCell ref="B62:D64"/>
-    <mergeCell ref="W68:X70"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:D4"/>
+    <mergeCell ref="E2:G4"/>
+    <mergeCell ref="H2:I4"/>
+    <mergeCell ref="J2:N4"/>
+    <mergeCell ref="O2:R4"/>
+    <mergeCell ref="S2:V4"/>
+    <mergeCell ref="W2:X4"/>
+    <mergeCell ref="Y2:AB4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:D7"/>
+    <mergeCell ref="E5:G7"/>
+    <mergeCell ref="H5:I7"/>
+    <mergeCell ref="J5:N7"/>
+    <mergeCell ref="O5:R7"/>
+    <mergeCell ref="S5:V7"/>
+    <mergeCell ref="W5:X7"/>
+    <mergeCell ref="Y5:AB7"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:D13"/>
+    <mergeCell ref="E11:G13"/>
+    <mergeCell ref="H11:I13"/>
+    <mergeCell ref="J11:N13"/>
+    <mergeCell ref="O11:R13"/>
+    <mergeCell ref="S11:V13"/>
+    <mergeCell ref="W11:X13"/>
+    <mergeCell ref="Y11:AB13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce2a9dd481ca40a5/Desktop/git/secret_stuff_miniapp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{EAA5244A-4873-4B1C-95EB-2450F5CC5E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30C9A077-8AC6-413E-A994-158EC19EEDAC}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{EAA5244A-4873-4B1C-95EB-2450F5CC5E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24F417C6-6431-4D2E-ABF3-B069A325FEC8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="324">
   <si>
     <t>id</t>
   </si>
@@ -951,9 +951,6 @@
   </si>
   <si>
     <t>{"черный": {"S":3, "M":3, "L":3, "XL"2}, "красный": {"S":1, "M":1, "L":1}}</t>
-  </si>
-  <si>
-    <t>{"черный": {"S":4, "M":4, "L":4, "XL"4}, "белый": {"S":1, "M":1, "L":1, "XL"1}}</t>
   </si>
   <si>
     <t>supball.png</t>
@@ -1699,14 +1696,14 @@
       </c>
       <c r="I2" s="60"/>
       <c r="J2" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K2" s="60"/>
       <c r="L2" s="60"/>
       <c r="M2" s="60"/>
       <c r="N2" s="60"/>
       <c r="O2" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="P2" s="60"/>
       <c r="Q2" s="60"/>
@@ -1722,7 +1719,7 @@
       </c>
       <c r="X2" s="60"/>
       <c r="Y2" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Z2" s="60"/>
       <c r="AA2" s="60"/>
@@ -1807,7 +1804,7 @@
       </c>
       <c r="I5" s="60"/>
       <c r="J5" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K5" s="60"/>
       <c r="L5" s="60"/>
@@ -1830,7 +1827,7 @@
       </c>
       <c r="X5" s="60"/>
       <c r="Y5" s="14" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Z5" s="60"/>
       <c r="AA5" s="60"/>
@@ -1915,7 +1912,7 @@
       </c>
       <c r="I8" s="60"/>
       <c r="J8" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K8" s="60"/>
       <c r="L8" s="60"/>
@@ -1938,7 +1935,7 @@
       </c>
       <c r="X8" s="60"/>
       <c r="Y8" s="14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Z8" s="60"/>
       <c r="AA8" s="60"/>
@@ -2023,7 +2020,7 @@
       </c>
       <c r="I11" s="60"/>
       <c r="J11" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K11" s="60"/>
       <c r="L11" s="60"/>
@@ -2046,7 +2043,7 @@
       </c>
       <c r="X11" s="60"/>
       <c r="Y11" s="14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Z11" s="60"/>
       <c r="AA11" s="60"/>
@@ -2131,7 +2128,7 @@
       </c>
       <c r="I14" s="60"/>
       <c r="J14" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K14" s="60"/>
       <c r="L14" s="60"/>
@@ -2154,7 +2151,7 @@
       </c>
       <c r="X14" s="60"/>
       <c r="Y14" s="14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Z14" s="60"/>
       <c r="AA14" s="60"/>
@@ -2239,7 +2236,7 @@
       </c>
       <c r="I17" s="60"/>
       <c r="J17" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K17" s="60"/>
       <c r="L17" s="60"/>
@@ -2262,7 +2259,7 @@
       </c>
       <c r="X17" s="60"/>
       <c r="Y17" s="14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Z17" s="60"/>
       <c r="AA17" s="60"/>
@@ -2347,7 +2344,7 @@
       </c>
       <c r="I20" s="60"/>
       <c r="J20" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K20" s="60"/>
       <c r="L20" s="60"/>
@@ -2370,7 +2367,7 @@
       </c>
       <c r="X20" s="60"/>
       <c r="Y20" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Z20" s="60"/>
       <c r="AA20" s="60"/>
